--- a/reports/selenium/test-results.xlsx
+++ b/reports/selenium/test-results.xlsx
@@ -30,7 +30,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/27/2026, 8:21:42 AM</t>
+    <t>7/27/2026, 8:26:57 AM</t>
   </si>
   <si>
     <t>Total Tests Executed</t>
@@ -1074,7 +1074,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>2000</v>
+        <v>2089</v>
       </c>
     </row>
   </sheetData>
@@ -1325,7 +1325,7 @@
         <v>31</v>
       </c>
       <c r="D2" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>32</v>
@@ -1342,7 +1342,7 @@
         <v>31</v>
       </c>
       <c r="D3" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>32</v>
@@ -1359,7 +1359,7 @@
         <v>31</v>
       </c>
       <c r="D4" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>32</v>
@@ -1376,7 +1376,7 @@
         <v>31</v>
       </c>
       <c r="D5" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>32</v>
@@ -1393,7 +1393,7 @@
         <v>31</v>
       </c>
       <c r="D6" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>32</v>
@@ -1410,7 +1410,7 @@
         <v>31</v>
       </c>
       <c r="D7" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>32</v>
@@ -1427,7 +1427,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>32</v>
@@ -1444,7 +1444,7 @@
         <v>31</v>
       </c>
       <c r="D9" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>32</v>
@@ -1461,7 +1461,7 @@
         <v>31</v>
       </c>
       <c r="D10" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>32</v>
@@ -1478,7 +1478,7 @@
         <v>31</v>
       </c>
       <c r="D11" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>32</v>
@@ -1495,7 +1495,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>32</v>
@@ -1512,7 +1512,7 @@
         <v>31</v>
       </c>
       <c r="D13" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>32</v>
@@ -1529,7 +1529,7 @@
         <v>31</v>
       </c>
       <c r="D14" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>32</v>
@@ -1546,7 +1546,7 @@
         <v>31</v>
       </c>
       <c r="D15" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>32</v>
@@ -1563,7 +1563,7 @@
         <v>31</v>
       </c>
       <c r="D16" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>32</v>
@@ -1580,7 +1580,7 @@
         <v>31</v>
       </c>
       <c r="D17" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>32</v>
@@ -1597,7 +1597,7 @@
         <v>31</v>
       </c>
       <c r="D18" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>32</v>
@@ -1614,7 +1614,7 @@
         <v>31</v>
       </c>
       <c r="D19" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>32</v>
@@ -1631,7 +1631,7 @@
         <v>31</v>
       </c>
       <c r="D20" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>32</v>
@@ -1648,7 +1648,7 @@
         <v>31</v>
       </c>
       <c r="D21" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>32</v>
@@ -1665,7 +1665,7 @@
         <v>31</v>
       </c>
       <c r="D22" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>32</v>
@@ -1682,7 +1682,7 @@
         <v>31</v>
       </c>
       <c r="D23" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>32</v>
@@ -1699,7 +1699,7 @@
         <v>31</v>
       </c>
       <c r="D24" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>32</v>
@@ -1716,7 +1716,7 @@
         <v>31</v>
       </c>
       <c r="D25" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>32</v>
@@ -1733,7 +1733,7 @@
         <v>31</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>32</v>
@@ -1750,7 +1750,7 @@
         <v>31</v>
       </c>
       <c r="D27" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>32</v>
@@ -1767,7 +1767,7 @@
         <v>31</v>
       </c>
       <c r="D28" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>32</v>
@@ -1784,7 +1784,7 @@
         <v>31</v>
       </c>
       <c r="D29" s="2">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>32</v>
@@ -1801,7 +1801,7 @@
         <v>31</v>
       </c>
       <c r="D30" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>32</v>
@@ -1818,7 +1818,7 @@
         <v>31</v>
       </c>
       <c r="D31" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>32</v>
@@ -1852,7 +1852,7 @@
         <v>31</v>
       </c>
       <c r="D33" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>32</v>
@@ -1869,7 +1869,7 @@
         <v>31</v>
       </c>
       <c r="D34" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>32</v>
@@ -1886,7 +1886,7 @@
         <v>31</v>
       </c>
       <c r="D35" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>32</v>
@@ -1903,7 +1903,7 @@
         <v>31</v>
       </c>
       <c r="D36" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>32</v>
@@ -1920,7 +1920,7 @@
         <v>31</v>
       </c>
       <c r="D37" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>32</v>
@@ -1937,7 +1937,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>32</v>
@@ -1971,7 +1971,7 @@
         <v>31</v>
       </c>
       <c r="D40" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>32</v>
@@ -1988,7 +1988,7 @@
         <v>31</v>
       </c>
       <c r="D41" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>32</v>
@@ -2005,7 +2005,7 @@
         <v>31</v>
       </c>
       <c r="D42" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>32</v>
@@ -2022,7 +2022,7 @@
         <v>31</v>
       </c>
       <c r="D43" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>32</v>
@@ -2039,7 +2039,7 @@
         <v>31</v>
       </c>
       <c r="D44" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>32</v>
@@ -2056,7 +2056,7 @@
         <v>31</v>
       </c>
       <c r="D45" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>32</v>
@@ -2073,7 +2073,7 @@
         <v>31</v>
       </c>
       <c r="D46" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>32</v>
@@ -2090,7 +2090,7 @@
         <v>31</v>
       </c>
       <c r="D47" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>32</v>
@@ -2107,7 +2107,7 @@
         <v>31</v>
       </c>
       <c r="D48" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>32</v>
@@ -2158,7 +2158,7 @@
         <v>31</v>
       </c>
       <c r="D51" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>32</v>
@@ -2175,7 +2175,7 @@
         <v>31</v>
       </c>
       <c r="D52" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>32</v>
@@ -2192,7 +2192,7 @@
         <v>31</v>
       </c>
       <c r="D53" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>32</v>
@@ -2209,7 +2209,7 @@
         <v>31</v>
       </c>
       <c r="D54" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>32</v>
@@ -2243,7 +2243,7 @@
         <v>31</v>
       </c>
       <c r="D56" s="2">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>32</v>
@@ -2260,7 +2260,7 @@
         <v>31</v>
       </c>
       <c r="D57" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>32</v>
@@ -2277,7 +2277,7 @@
         <v>31</v>
       </c>
       <c r="D58" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>32</v>
@@ -2294,7 +2294,7 @@
         <v>31</v>
       </c>
       <c r="D59" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>32</v>
@@ -2311,7 +2311,7 @@
         <v>31</v>
       </c>
       <c r="D60" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>32</v>
@@ -2328,7 +2328,7 @@
         <v>31</v>
       </c>
       <c r="D61" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>32</v>
@@ -2345,7 +2345,7 @@
         <v>31</v>
       </c>
       <c r="D62" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>32</v>
@@ -2362,7 +2362,7 @@
         <v>31</v>
       </c>
       <c r="D63" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>32</v>
@@ -2379,7 +2379,7 @@
         <v>31</v>
       </c>
       <c r="D64" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>32</v>
@@ -2396,7 +2396,7 @@
         <v>31</v>
       </c>
       <c r="D65" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>32</v>
@@ -2413,7 +2413,7 @@
         <v>31</v>
       </c>
       <c r="D66" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>32</v>
@@ -2430,7 +2430,7 @@
         <v>31</v>
       </c>
       <c r="D67" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>32</v>
@@ -2447,7 +2447,7 @@
         <v>31</v>
       </c>
       <c r="D68" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>32</v>
@@ -2464,7 +2464,7 @@
         <v>31</v>
       </c>
       <c r="D69" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>32</v>
@@ -2481,7 +2481,7 @@
         <v>31</v>
       </c>
       <c r="D70" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>32</v>
@@ -2498,7 +2498,7 @@
         <v>31</v>
       </c>
       <c r="D71" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>32</v>
@@ -2515,7 +2515,7 @@
         <v>31</v>
       </c>
       <c r="D72" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>32</v>
@@ -2532,7 +2532,7 @@
         <v>31</v>
       </c>
       <c r="D73" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>32</v>
@@ -2549,7 +2549,7 @@
         <v>31</v>
       </c>
       <c r="D74" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>32</v>
@@ -2566,7 +2566,7 @@
         <v>31</v>
       </c>
       <c r="D75" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>32</v>
@@ -2583,7 +2583,7 @@
         <v>31</v>
       </c>
       <c r="D76" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>32</v>
@@ -2600,7 +2600,7 @@
         <v>31</v>
       </c>
       <c r="D77" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>32</v>
@@ -2617,7 +2617,7 @@
         <v>31</v>
       </c>
       <c r="D78" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>32</v>
@@ -2634,7 +2634,7 @@
         <v>31</v>
       </c>
       <c r="D79" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>32</v>
@@ -2651,7 +2651,7 @@
         <v>31</v>
       </c>
       <c r="D80" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>32</v>
@@ -2668,7 +2668,7 @@
         <v>31</v>
       </c>
       <c r="D81" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>32</v>
@@ -2685,7 +2685,7 @@
         <v>31</v>
       </c>
       <c r="D82" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>32</v>
@@ -2702,7 +2702,7 @@
         <v>31</v>
       </c>
       <c r="D83" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>32</v>
@@ -2719,7 +2719,7 @@
         <v>31</v>
       </c>
       <c r="D84" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>32</v>
@@ -2736,7 +2736,7 @@
         <v>31</v>
       </c>
       <c r="D85" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>32</v>
@@ -2753,7 +2753,7 @@
         <v>31</v>
       </c>
       <c r="D86" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>32</v>
@@ -2770,7 +2770,7 @@
         <v>31</v>
       </c>
       <c r="D87" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>32</v>
@@ -2804,7 +2804,7 @@
         <v>31</v>
       </c>
       <c r="D89" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>32</v>
@@ -2821,7 +2821,7 @@
         <v>31</v>
       </c>
       <c r="D90" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>32</v>
@@ -2838,7 +2838,7 @@
         <v>31</v>
       </c>
       <c r="D91" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>32</v>
@@ -2855,7 +2855,7 @@
         <v>31</v>
       </c>
       <c r="D92" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>32</v>
@@ -2872,7 +2872,7 @@
         <v>31</v>
       </c>
       <c r="D93" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>32</v>
@@ -2889,7 +2889,7 @@
         <v>31</v>
       </c>
       <c r="D94" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>32</v>
@@ -2906,7 +2906,7 @@
         <v>31</v>
       </c>
       <c r="D95" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>32</v>
@@ -2923,7 +2923,7 @@
         <v>31</v>
       </c>
       <c r="D96" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>32</v>
@@ -2940,7 +2940,7 @@
         <v>31</v>
       </c>
       <c r="D97" s="2">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>32</v>
@@ -2957,7 +2957,7 @@
         <v>31</v>
       </c>
       <c r="D98" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>32</v>
@@ -2974,7 +2974,7 @@
         <v>31</v>
       </c>
       <c r="D99" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>32</v>
@@ -2991,7 +2991,7 @@
         <v>31</v>
       </c>
       <c r="D100" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>32</v>
@@ -3008,7 +3008,7 @@
         <v>31</v>
       </c>
       <c r="D101" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>32</v>
@@ -3025,7 +3025,7 @@
         <v>31</v>
       </c>
       <c r="D102" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>32</v>
@@ -3042,7 +3042,7 @@
         <v>31</v>
       </c>
       <c r="D103" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>32</v>
@@ -3059,7 +3059,7 @@
         <v>31</v>
       </c>
       <c r="D104" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>32</v>
@@ -3076,7 +3076,7 @@
         <v>31</v>
       </c>
       <c r="D105" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>32</v>
@@ -3093,7 +3093,7 @@
         <v>31</v>
       </c>
       <c r="D106" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>32</v>
@@ -3110,7 +3110,7 @@
         <v>31</v>
       </c>
       <c r="D107" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>32</v>
@@ -3127,7 +3127,7 @@
         <v>31</v>
       </c>
       <c r="D108" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>32</v>
@@ -3144,7 +3144,7 @@
         <v>31</v>
       </c>
       <c r="D109" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>32</v>
@@ -3161,7 +3161,7 @@
         <v>31</v>
       </c>
       <c r="D110" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>32</v>
@@ -3178,7 +3178,7 @@
         <v>31</v>
       </c>
       <c r="D111" s="2">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>32</v>
@@ -3195,7 +3195,7 @@
         <v>31</v>
       </c>
       <c r="D112" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>32</v>
@@ -3212,7 +3212,7 @@
         <v>31</v>
       </c>
       <c r="D113" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>32</v>
@@ -3229,7 +3229,7 @@
         <v>31</v>
       </c>
       <c r="D114" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>32</v>
@@ -3246,7 +3246,7 @@
         <v>31</v>
       </c>
       <c r="D115" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>32</v>
@@ -3263,7 +3263,7 @@
         <v>31</v>
       </c>
       <c r="D116" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>32</v>
@@ -3280,7 +3280,7 @@
         <v>31</v>
       </c>
       <c r="D117" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>32</v>
@@ -3297,7 +3297,7 @@
         <v>31</v>
       </c>
       <c r="D118" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>32</v>
@@ -3314,7 +3314,7 @@
         <v>31</v>
       </c>
       <c r="D119" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>32</v>
@@ -3331,7 +3331,7 @@
         <v>31</v>
       </c>
       <c r="D120" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>32</v>
@@ -3348,7 +3348,7 @@
         <v>31</v>
       </c>
       <c r="D121" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>32</v>
@@ -3365,7 +3365,7 @@
         <v>31</v>
       </c>
       <c r="D122" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>32</v>
@@ -3382,7 +3382,7 @@
         <v>31</v>
       </c>
       <c r="D123" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>32</v>
@@ -3399,7 +3399,7 @@
         <v>31</v>
       </c>
       <c r="D124" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>32</v>
@@ -3416,7 +3416,7 @@
         <v>31</v>
       </c>
       <c r="D125" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>32</v>
@@ -3433,7 +3433,7 @@
         <v>31</v>
       </c>
       <c r="D126" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>32</v>
@@ -3450,7 +3450,7 @@
         <v>31</v>
       </c>
       <c r="D127" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>32</v>
@@ -3467,7 +3467,7 @@
         <v>31</v>
       </c>
       <c r="D128" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>32</v>
@@ -3484,7 +3484,7 @@
         <v>31</v>
       </c>
       <c r="D129" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>32</v>
@@ -3501,7 +3501,7 @@
         <v>31</v>
       </c>
       <c r="D130" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>32</v>
@@ -3518,7 +3518,7 @@
         <v>31</v>
       </c>
       <c r="D131" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>32</v>
@@ -3535,7 +3535,7 @@
         <v>31</v>
       </c>
       <c r="D132" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>32</v>
@@ -3552,7 +3552,7 @@
         <v>31</v>
       </c>
       <c r="D133" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>32</v>
@@ -3569,7 +3569,7 @@
         <v>31</v>
       </c>
       <c r="D134" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>32</v>
@@ -3586,7 +3586,7 @@
         <v>31</v>
       </c>
       <c r="D135" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>32</v>
@@ -3603,7 +3603,7 @@
         <v>31</v>
       </c>
       <c r="D136" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>32</v>
@@ -3620,7 +3620,7 @@
         <v>31</v>
       </c>
       <c r="D137" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>32</v>
@@ -3637,7 +3637,7 @@
         <v>31</v>
       </c>
       <c r="D138" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>32</v>
@@ -3654,7 +3654,7 @@
         <v>31</v>
       </c>
       <c r="D139" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>32</v>
@@ -3671,7 +3671,7 @@
         <v>31</v>
       </c>
       <c r="D140" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>32</v>
@@ -3688,7 +3688,7 @@
         <v>31</v>
       </c>
       <c r="D141" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>32</v>
@@ -3705,7 +3705,7 @@
         <v>31</v>
       </c>
       <c r="D142" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>32</v>
@@ -3722,7 +3722,7 @@
         <v>31</v>
       </c>
       <c r="D143" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>32</v>
@@ -3756,7 +3756,7 @@
         <v>31</v>
       </c>
       <c r="D145" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>32</v>
@@ -3773,7 +3773,7 @@
         <v>31</v>
       </c>
       <c r="D146" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>32</v>
@@ -3790,7 +3790,7 @@
         <v>31</v>
       </c>
       <c r="D147" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>32</v>
@@ -3807,7 +3807,7 @@
         <v>31</v>
       </c>
       <c r="D148" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>32</v>
@@ -3824,7 +3824,7 @@
         <v>31</v>
       </c>
       <c r="D149" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>32</v>
@@ -3841,7 +3841,7 @@
         <v>31</v>
       </c>
       <c r="D150" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>32</v>
@@ -3858,7 +3858,7 @@
         <v>31</v>
       </c>
       <c r="D151" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>32</v>
@@ -3875,7 +3875,7 @@
         <v>31</v>
       </c>
       <c r="D152" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>32</v>
@@ -3892,7 +3892,7 @@
         <v>31</v>
       </c>
       <c r="D153" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>32</v>
@@ -3909,7 +3909,7 @@
         <v>31</v>
       </c>
       <c r="D154" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>32</v>
@@ -3926,7 +3926,7 @@
         <v>31</v>
       </c>
       <c r="D155" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>32</v>
@@ -3943,7 +3943,7 @@
         <v>31</v>
       </c>
       <c r="D156" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>32</v>
@@ -3960,7 +3960,7 @@
         <v>31</v>
       </c>
       <c r="D157" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>32</v>
@@ -3977,7 +3977,7 @@
         <v>31</v>
       </c>
       <c r="D158" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>32</v>
@@ -3994,7 +3994,7 @@
         <v>31</v>
       </c>
       <c r="D159" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>32</v>
@@ -4011,7 +4011,7 @@
         <v>31</v>
       </c>
       <c r="D160" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>32</v>
@@ -4028,7 +4028,7 @@
         <v>31</v>
       </c>
       <c r="D161" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>32</v>

--- a/reports/selenium/test-results.xlsx
+++ b/reports/selenium/test-results.xlsx
@@ -30,7 +30,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/27/2026, 8:30:34 AM</t>
+    <t>7/27/2026, 8:35:34 AM</t>
   </si>
   <si>
     <t>Total Tests Executed</t>
@@ -2721,7 +2721,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>8724</v>
+        <v>8748</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3261,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>49</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="2">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>49</v>
@@ -3295,7 +3295,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -3312,7 +3312,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>49</v>
@@ -3329,7 +3329,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -3346,7 +3346,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -3363,7 +3363,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>49</v>
@@ -3380,7 +3380,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -3397,7 +3397,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>49</v>
@@ -3414,7 +3414,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -3431,7 +3431,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -3448,7 +3448,7 @@
         <v>48</v>
       </c>
       <c r="D13" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>49</v>
@@ -3465,7 +3465,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>49</v>
@@ -3482,7 +3482,7 @@
         <v>48</v>
       </c>
       <c r="D15" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>49</v>
@@ -3499,7 +3499,7 @@
         <v>48</v>
       </c>
       <c r="D16" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>49</v>
@@ -3516,7 +3516,7 @@
         <v>48</v>
       </c>
       <c r="D17" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>49</v>
@@ -3533,7 +3533,7 @@
         <v>48</v>
       </c>
       <c r="D18" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>49</v>
@@ -3550,7 +3550,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>49</v>
@@ -3567,7 +3567,7 @@
         <v>48</v>
       </c>
       <c r="D20" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>49</v>
@@ -3584,7 +3584,7 @@
         <v>48</v>
       </c>
       <c r="D21" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>49</v>
@@ -3601,7 +3601,7 @@
         <v>48</v>
       </c>
       <c r="D22" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>49</v>
@@ -3618,7 +3618,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>49</v>
@@ -3635,7 +3635,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>49</v>
@@ -3652,7 +3652,7 @@
         <v>48</v>
       </c>
       <c r="D25" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>49</v>
@@ -3669,7 +3669,7 @@
         <v>48</v>
       </c>
       <c r="D26" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>49</v>
@@ -3686,7 +3686,7 @@
         <v>48</v>
       </c>
       <c r="D27" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>49</v>
@@ -3703,7 +3703,7 @@
         <v>48</v>
       </c>
       <c r="D28" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>49</v>
@@ -3720,7 +3720,7 @@
         <v>48</v>
       </c>
       <c r="D29" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>49</v>
@@ -3737,7 +3737,7 @@
         <v>48</v>
       </c>
       <c r="D30" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>49</v>
@@ -3771,7 +3771,7 @@
         <v>48</v>
       </c>
       <c r="D32" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>49</v>
@@ -3788,7 +3788,7 @@
         <v>48</v>
       </c>
       <c r="D33" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>49</v>
@@ -3805,7 +3805,7 @@
         <v>48</v>
       </c>
       <c r="D34" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>49</v>
@@ -3822,7 +3822,7 @@
         <v>48</v>
       </c>
       <c r="D35" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>49</v>
@@ -3839,7 +3839,7 @@
         <v>48</v>
       </c>
       <c r="D36" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>49</v>
@@ -3856,7 +3856,7 @@
         <v>48</v>
       </c>
       <c r="D37" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>49</v>
@@ -3873,7 +3873,7 @@
         <v>48</v>
       </c>
       <c r="D38" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>49</v>
@@ -3890,7 +3890,7 @@
         <v>48</v>
       </c>
       <c r="D39" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>49</v>
@@ -3907,7 +3907,7 @@
         <v>48</v>
       </c>
       <c r="D40" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>49</v>
@@ -3924,7 +3924,7 @@
         <v>48</v>
       </c>
       <c r="D41" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>49</v>
@@ -3941,7 +3941,7 @@
         <v>48</v>
       </c>
       <c r="D42" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>49</v>
@@ -3958,7 +3958,7 @@
         <v>48</v>
       </c>
       <c r="D43" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>49</v>
@@ -3975,7 +3975,7 @@
         <v>48</v>
       </c>
       <c r="D44" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>49</v>
@@ -3992,7 +3992,7 @@
         <v>48</v>
       </c>
       <c r="D45" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>49</v>
@@ -4009,7 +4009,7 @@
         <v>48</v>
       </c>
       <c r="D46" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>49</v>
@@ -4043,7 +4043,7 @@
         <v>48</v>
       </c>
       <c r="D48" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>49</v>
@@ -4060,7 +4060,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>49</v>
@@ -4077,7 +4077,7 @@
         <v>48</v>
       </c>
       <c r="D50" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>49</v>
@@ -4094,7 +4094,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>49</v>
@@ -4111,7 +4111,7 @@
         <v>48</v>
       </c>
       <c r="D52" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>49</v>
@@ -4128,7 +4128,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>49</v>
@@ -4145,7 +4145,7 @@
         <v>48</v>
       </c>
       <c r="D54" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>49</v>
@@ -4162,7 +4162,7 @@
         <v>48</v>
       </c>
       <c r="D55" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>49</v>
@@ -4179,7 +4179,7 @@
         <v>48</v>
       </c>
       <c r="D56" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>49</v>
@@ -4196,7 +4196,7 @@
         <v>48</v>
       </c>
       <c r="D57" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>49</v>
@@ -4213,7 +4213,7 @@
         <v>48</v>
       </c>
       <c r="D58" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>49</v>
@@ -4230,7 +4230,7 @@
         <v>48</v>
       </c>
       <c r="D59" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>49</v>
@@ -4247,7 +4247,7 @@
         <v>48</v>
       </c>
       <c r="D60" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>49</v>
@@ -4264,7 +4264,7 @@
         <v>48</v>
       </c>
       <c r="D61" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>49</v>
@@ -4281,7 +4281,7 @@
         <v>48</v>
       </c>
       <c r="D62" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>49</v>
@@ -4298,7 +4298,7 @@
         <v>48</v>
       </c>
       <c r="D63" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>49</v>
@@ -4315,7 +4315,7 @@
         <v>48</v>
       </c>
       <c r="D64" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>49</v>
@@ -4332,7 +4332,7 @@
         <v>48</v>
       </c>
       <c r="D65" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>49</v>
@@ -4349,7 +4349,7 @@
         <v>48</v>
       </c>
       <c r="D66" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>49</v>
@@ -4366,7 +4366,7 @@
         <v>48</v>
       </c>
       <c r="D67" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>49</v>
@@ -4383,7 +4383,7 @@
         <v>48</v>
       </c>
       <c r="D68" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>49</v>
@@ -4400,7 +4400,7 @@
         <v>48</v>
       </c>
       <c r="D69" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>49</v>
@@ -4417,7 +4417,7 @@
         <v>48</v>
       </c>
       <c r="D70" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>49</v>
@@ -4434,7 +4434,7 @@
         <v>48</v>
       </c>
       <c r="D71" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>49</v>
@@ -4451,7 +4451,7 @@
         <v>48</v>
       </c>
       <c r="D72" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>49</v>
@@ -4468,7 +4468,7 @@
         <v>48</v>
       </c>
       <c r="D73" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>49</v>
@@ -4485,7 +4485,7 @@
         <v>48</v>
       </c>
       <c r="D74" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>49</v>
@@ -4519,7 +4519,7 @@
         <v>48</v>
       </c>
       <c r="D76" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>49</v>
@@ -4536,7 +4536,7 @@
         <v>48</v>
       </c>
       <c r="D77" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>49</v>
@@ -4553,7 +4553,7 @@
         <v>48</v>
       </c>
       <c r="D78" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>49</v>
@@ -4570,7 +4570,7 @@
         <v>48</v>
       </c>
       <c r="D79" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>49</v>
@@ -4587,7 +4587,7 @@
         <v>48</v>
       </c>
       <c r="D80" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>49</v>
@@ -4604,7 +4604,7 @@
         <v>48</v>
       </c>
       <c r="D81" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>49</v>
@@ -4621,7 +4621,7 @@
         <v>48</v>
       </c>
       <c r="D82" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>49</v>
@@ -4638,7 +4638,7 @@
         <v>48</v>
       </c>
       <c r="D83" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>49</v>
@@ -4655,7 +4655,7 @@
         <v>48</v>
       </c>
       <c r="D84" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>49</v>
@@ -4672,7 +4672,7 @@
         <v>48</v>
       </c>
       <c r="D85" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>49</v>
@@ -4689,7 +4689,7 @@
         <v>48</v>
       </c>
       <c r="D86" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>49</v>
@@ -4723,7 +4723,7 @@
         <v>48</v>
       </c>
       <c r="D88" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>49</v>
@@ -4740,7 +4740,7 @@
         <v>48</v>
       </c>
       <c r="D89" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>49</v>
@@ -4757,7 +4757,7 @@
         <v>48</v>
       </c>
       <c r="D90" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>49</v>
@@ -4774,7 +4774,7 @@
         <v>48</v>
       </c>
       <c r="D91" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>49</v>
@@ -4791,7 +4791,7 @@
         <v>48</v>
       </c>
       <c r="D92" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>49</v>
@@ -4808,7 +4808,7 @@
         <v>48</v>
       </c>
       <c r="D93" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>49</v>
@@ -4825,7 +4825,7 @@
         <v>48</v>
       </c>
       <c r="D94" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>49</v>
@@ -4842,7 +4842,7 @@
         <v>48</v>
       </c>
       <c r="D95" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>49</v>
@@ -4859,7 +4859,7 @@
         <v>48</v>
       </c>
       <c r="D96" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>49</v>
@@ -4876,7 +4876,7 @@
         <v>48</v>
       </c>
       <c r="D97" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>49</v>
@@ -4893,7 +4893,7 @@
         <v>48</v>
       </c>
       <c r="D98" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>49</v>
@@ -4910,7 +4910,7 @@
         <v>48</v>
       </c>
       <c r="D99" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>49</v>
@@ -4927,7 +4927,7 @@
         <v>48</v>
       </c>
       <c r="D100" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>49</v>
@@ -4944,7 +4944,7 @@
         <v>48</v>
       </c>
       <c r="D101" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>49</v>
@@ -4961,7 +4961,7 @@
         <v>48</v>
       </c>
       <c r="D102" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>49</v>
@@ -4978,7 +4978,7 @@
         <v>48</v>
       </c>
       <c r="D103" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>49</v>
@@ -4995,7 +4995,7 @@
         <v>48</v>
       </c>
       <c r="D104" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>49</v>
@@ -5012,7 +5012,7 @@
         <v>48</v>
       </c>
       <c r="D105" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>49</v>
@@ -5029,7 +5029,7 @@
         <v>48</v>
       </c>
       <c r="D106" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>49</v>
@@ -5046,7 +5046,7 @@
         <v>48</v>
       </c>
       <c r="D107" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>49</v>
@@ -5063,7 +5063,7 @@
         <v>48</v>
       </c>
       <c r="D108" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>49</v>
@@ -5080,7 +5080,7 @@
         <v>48</v>
       </c>
       <c r="D109" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>49</v>
@@ -5097,7 +5097,7 @@
         <v>48</v>
       </c>
       <c r="D110" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>49</v>
@@ -5114,7 +5114,7 @@
         <v>48</v>
       </c>
       <c r="D111" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>49</v>
@@ -5131,7 +5131,7 @@
         <v>48</v>
       </c>
       <c r="D112" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>49</v>
@@ -5148,7 +5148,7 @@
         <v>48</v>
       </c>
       <c r="D113" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>49</v>
@@ -5165,7 +5165,7 @@
         <v>48</v>
       </c>
       <c r="D114" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>49</v>
@@ -5182,7 +5182,7 @@
         <v>48</v>
       </c>
       <c r="D115" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>49</v>
@@ -5199,7 +5199,7 @@
         <v>48</v>
       </c>
       <c r="D116" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>49</v>
@@ -5216,7 +5216,7 @@
         <v>48</v>
       </c>
       <c r="D117" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>49</v>
@@ -5233,7 +5233,7 @@
         <v>48</v>
       </c>
       <c r="D118" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>49</v>
@@ -5250,7 +5250,7 @@
         <v>48</v>
       </c>
       <c r="D119" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>49</v>
@@ -5267,7 +5267,7 @@
         <v>48</v>
       </c>
       <c r="D120" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>49</v>
@@ -5284,7 +5284,7 @@
         <v>48</v>
       </c>
       <c r="D121" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>49</v>
@@ -5301,7 +5301,7 @@
         <v>48</v>
       </c>
       <c r="D122" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>49</v>
@@ -5318,7 +5318,7 @@
         <v>48</v>
       </c>
       <c r="D123" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>49</v>
@@ -5335,7 +5335,7 @@
         <v>48</v>
       </c>
       <c r="D124" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>49</v>
@@ -5352,7 +5352,7 @@
         <v>48</v>
       </c>
       <c r="D125" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>49</v>
@@ -5369,7 +5369,7 @@
         <v>48</v>
       </c>
       <c r="D126" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>49</v>
@@ -5403,7 +5403,7 @@
         <v>48</v>
       </c>
       <c r="D128" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>49</v>
@@ -5420,7 +5420,7 @@
         <v>48</v>
       </c>
       <c r="D129" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>49</v>
@@ -5437,7 +5437,7 @@
         <v>48</v>
       </c>
       <c r="D130" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>49</v>
@@ -5454,7 +5454,7 @@
         <v>48</v>
       </c>
       <c r="D131" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>49</v>
@@ -5471,7 +5471,7 @@
         <v>48</v>
       </c>
       <c r="D132" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>49</v>
@@ -5488,7 +5488,7 @@
         <v>48</v>
       </c>
       <c r="D133" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>49</v>
@@ -5522,7 +5522,7 @@
         <v>48</v>
       </c>
       <c r="D135" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>49</v>
@@ -5556,7 +5556,7 @@
         <v>48</v>
       </c>
       <c r="D137" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>49</v>
@@ -5573,7 +5573,7 @@
         <v>48</v>
       </c>
       <c r="D138" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>49</v>
@@ -5590,7 +5590,7 @@
         <v>48</v>
       </c>
       <c r="D139" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>49</v>
@@ -5607,7 +5607,7 @@
         <v>48</v>
       </c>
       <c r="D140" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>49</v>
@@ -5624,7 +5624,7 @@
         <v>48</v>
       </c>
       <c r="D141" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>49</v>
@@ -5658,7 +5658,7 @@
         <v>48</v>
       </c>
       <c r="D143" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>49</v>
@@ -5675,7 +5675,7 @@
         <v>48</v>
       </c>
       <c r="D144" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>49</v>
@@ -5709,7 +5709,7 @@
         <v>48</v>
       </c>
       <c r="D146" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>49</v>
@@ -5726,7 +5726,7 @@
         <v>48</v>
       </c>
       <c r="D147" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>49</v>
@@ -5743,7 +5743,7 @@
         <v>48</v>
       </c>
       <c r="D148" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>49</v>
@@ -5760,7 +5760,7 @@
         <v>48</v>
       </c>
       <c r="D149" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>49</v>
@@ -5777,7 +5777,7 @@
         <v>48</v>
       </c>
       <c r="D150" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>49</v>
@@ -5794,7 +5794,7 @@
         <v>48</v>
       </c>
       <c r="D151" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>49</v>
@@ -5811,7 +5811,7 @@
         <v>48</v>
       </c>
       <c r="D152" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>49</v>
@@ -5828,7 +5828,7 @@
         <v>48</v>
       </c>
       <c r="D153" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>49</v>
@@ -5845,7 +5845,7 @@
         <v>48</v>
       </c>
       <c r="D154" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>49</v>
@@ -5879,7 +5879,7 @@
         <v>48</v>
       </c>
       <c r="D156" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>49</v>
@@ -5896,7 +5896,7 @@
         <v>48</v>
       </c>
       <c r="D157" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>49</v>
@@ -5913,7 +5913,7 @@
         <v>48</v>
       </c>
       <c r="D158" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>49</v>
@@ -5930,7 +5930,7 @@
         <v>48</v>
       </c>
       <c r="D159" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>49</v>
@@ -5947,7 +5947,7 @@
         <v>48</v>
       </c>
       <c r="D160" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>49</v>
@@ -5964,7 +5964,7 @@
         <v>48</v>
       </c>
       <c r="D161" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>49</v>
@@ -5981,7 +5981,7 @@
         <v>48</v>
       </c>
       <c r="D162" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>49</v>
@@ -6015,7 +6015,7 @@
         <v>48</v>
       </c>
       <c r="D164" s="2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>49</v>
@@ -6032,7 +6032,7 @@
         <v>48</v>
       </c>
       <c r="D165" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>49</v>
@@ -6049,7 +6049,7 @@
         <v>48</v>
       </c>
       <c r="D166" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>49</v>
@@ -6066,7 +6066,7 @@
         <v>48</v>
       </c>
       <c r="D167" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E167" s="2" t="s">
         <v>49</v>
@@ -6083,7 +6083,7 @@
         <v>48</v>
       </c>
       <c r="D168" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>49</v>
@@ -6100,7 +6100,7 @@
         <v>48</v>
       </c>
       <c r="D169" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>49</v>
@@ -6117,7 +6117,7 @@
         <v>48</v>
       </c>
       <c r="D170" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>49</v>
@@ -6134,7 +6134,7 @@
         <v>48</v>
       </c>
       <c r="D171" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>49</v>
@@ -6151,7 +6151,7 @@
         <v>48</v>
       </c>
       <c r="D172" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>49</v>
@@ -6168,7 +6168,7 @@
         <v>48</v>
       </c>
       <c r="D173" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>49</v>
@@ -6185,7 +6185,7 @@
         <v>48</v>
       </c>
       <c r="D174" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>49</v>
@@ -6202,7 +6202,7 @@
         <v>48</v>
       </c>
       <c r="D175" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>49</v>
@@ -6219,7 +6219,7 @@
         <v>48</v>
       </c>
       <c r="D176" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>49</v>
@@ -6236,7 +6236,7 @@
         <v>48</v>
       </c>
       <c r="D177" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>49</v>
@@ -6253,7 +6253,7 @@
         <v>48</v>
       </c>
       <c r="D178" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>49</v>
@@ -6270,7 +6270,7 @@
         <v>48</v>
       </c>
       <c r="D179" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>49</v>
@@ -6287,7 +6287,7 @@
         <v>48</v>
       </c>
       <c r="D180" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>49</v>
@@ -6304,7 +6304,7 @@
         <v>48</v>
       </c>
       <c r="D181" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>49</v>
@@ -6321,7 +6321,7 @@
         <v>48</v>
       </c>
       <c r="D182" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>49</v>
@@ -6338,7 +6338,7 @@
         <v>48</v>
       </c>
       <c r="D183" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>49</v>
@@ -6355,7 +6355,7 @@
         <v>48</v>
       </c>
       <c r="D184" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>49</v>
@@ -6372,7 +6372,7 @@
         <v>48</v>
       </c>
       <c r="D185" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>49</v>
@@ -6389,7 +6389,7 @@
         <v>48</v>
       </c>
       <c r="D186" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>49</v>
@@ -6406,7 +6406,7 @@
         <v>48</v>
       </c>
       <c r="D187" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>49</v>
@@ -6423,7 +6423,7 @@
         <v>48</v>
       </c>
       <c r="D188" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>49</v>
@@ -6440,7 +6440,7 @@
         <v>48</v>
       </c>
       <c r="D189" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>49</v>
@@ -6457,7 +6457,7 @@
         <v>48</v>
       </c>
       <c r="D190" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>49</v>
@@ -6474,7 +6474,7 @@
         <v>48</v>
       </c>
       <c r="D191" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>49</v>
@@ -6491,7 +6491,7 @@
         <v>48</v>
       </c>
       <c r="D192" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>49</v>
@@ -6508,7 +6508,7 @@
         <v>48</v>
       </c>
       <c r="D193" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>49</v>
@@ -6525,7 +6525,7 @@
         <v>48</v>
       </c>
       <c r="D194" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E194" s="2" t="s">
         <v>49</v>
@@ -6542,7 +6542,7 @@
         <v>48</v>
       </c>
       <c r="D195" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>49</v>
@@ -6559,7 +6559,7 @@
         <v>48</v>
       </c>
       <c r="D196" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>49</v>
@@ -6576,7 +6576,7 @@
         <v>48</v>
       </c>
       <c r="D197" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>49</v>
@@ -6593,7 +6593,7 @@
         <v>48</v>
       </c>
       <c r="D198" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>49</v>
@@ -6610,7 +6610,7 @@
         <v>48</v>
       </c>
       <c r="D199" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>49</v>
@@ -6644,7 +6644,7 @@
         <v>48</v>
       </c>
       <c r="D201" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>49</v>
@@ -6678,7 +6678,7 @@
         <v>48</v>
       </c>
       <c r="D203" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>49</v>
@@ -6695,7 +6695,7 @@
         <v>48</v>
       </c>
       <c r="D204" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E204" s="2" t="s">
         <v>49</v>
@@ -6712,7 +6712,7 @@
         <v>48</v>
       </c>
       <c r="D205" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>49</v>
@@ -6746,7 +6746,7 @@
         <v>48</v>
       </c>
       <c r="D207" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>49</v>
@@ -6763,7 +6763,7 @@
         <v>48</v>
       </c>
       <c r="D208" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>49</v>
@@ -6780,7 +6780,7 @@
         <v>48</v>
       </c>
       <c r="D209" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>49</v>
@@ -6797,7 +6797,7 @@
         <v>48</v>
       </c>
       <c r="D210" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>49</v>
@@ -6814,7 +6814,7 @@
         <v>48</v>
       </c>
       <c r="D211" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>49</v>
@@ -6831,7 +6831,7 @@
         <v>48</v>
       </c>
       <c r="D212" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E212" s="2" t="s">
         <v>49</v>
@@ -6848,7 +6848,7 @@
         <v>48</v>
       </c>
       <c r="D213" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>49</v>
@@ -6865,7 +6865,7 @@
         <v>48</v>
       </c>
       <c r="D214" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>49</v>
@@ -6882,7 +6882,7 @@
         <v>48</v>
       </c>
       <c r="D215" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>49</v>
@@ -6899,7 +6899,7 @@
         <v>48</v>
       </c>
       <c r="D216" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>49</v>
@@ -6916,7 +6916,7 @@
         <v>48</v>
       </c>
       <c r="D217" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>49</v>
@@ -6933,7 +6933,7 @@
         <v>48</v>
       </c>
       <c r="D218" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>49</v>
@@ -6967,7 +6967,7 @@
         <v>48</v>
       </c>
       <c r="D220" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>49</v>
@@ -6984,7 +6984,7 @@
         <v>48</v>
       </c>
       <c r="D221" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>49</v>
@@ -7001,7 +7001,7 @@
         <v>48</v>
       </c>
       <c r="D222" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>49</v>
@@ -7018,7 +7018,7 @@
         <v>48</v>
       </c>
       <c r="D223" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>49</v>
@@ -7035,7 +7035,7 @@
         <v>48</v>
       </c>
       <c r="D224" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E224" s="2" t="s">
         <v>49</v>
@@ -7052,7 +7052,7 @@
         <v>48</v>
       </c>
       <c r="D225" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>49</v>
@@ -7069,7 +7069,7 @@
         <v>48</v>
       </c>
       <c r="D226" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>49</v>
@@ -7086,7 +7086,7 @@
         <v>48</v>
       </c>
       <c r="D227" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>49</v>
@@ -7103,7 +7103,7 @@
         <v>48</v>
       </c>
       <c r="D228" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>49</v>
@@ -7120,7 +7120,7 @@
         <v>48</v>
       </c>
       <c r="D229" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>49</v>
@@ -7137,7 +7137,7 @@
         <v>48</v>
       </c>
       <c r="D230" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>49</v>
@@ -7154,7 +7154,7 @@
         <v>48</v>
       </c>
       <c r="D231" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>49</v>
@@ -7171,7 +7171,7 @@
         <v>48</v>
       </c>
       <c r="D232" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>49</v>
@@ -7188,7 +7188,7 @@
         <v>48</v>
       </c>
       <c r="D233" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>49</v>
@@ -7222,7 +7222,7 @@
         <v>48</v>
       </c>
       <c r="D235" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>49</v>
@@ -7239,7 +7239,7 @@
         <v>48</v>
       </c>
       <c r="D236" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>49</v>
@@ -7256,7 +7256,7 @@
         <v>48</v>
       </c>
       <c r="D237" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>49</v>
@@ -7273,7 +7273,7 @@
         <v>48</v>
       </c>
       <c r="D238" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>49</v>
@@ -7290,7 +7290,7 @@
         <v>48</v>
       </c>
       <c r="D239" s="2">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>49</v>
@@ -7307,7 +7307,7 @@
         <v>48</v>
       </c>
       <c r="D240" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>49</v>
@@ -7324,7 +7324,7 @@
         <v>48</v>
       </c>
       <c r="D241" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>49</v>
@@ -7341,7 +7341,7 @@
         <v>48</v>
       </c>
       <c r="D242" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>49</v>
@@ -7358,7 +7358,7 @@
         <v>48</v>
       </c>
       <c r="D243" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>49</v>
@@ -7375,7 +7375,7 @@
         <v>48</v>
       </c>
       <c r="D244" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>49</v>
@@ -7392,7 +7392,7 @@
         <v>48</v>
       </c>
       <c r="D245" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>49</v>
@@ -7409,7 +7409,7 @@
         <v>48</v>
       </c>
       <c r="D246" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>49</v>
@@ -7426,7 +7426,7 @@
         <v>48</v>
       </c>
       <c r="D247" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>49</v>
@@ -7443,7 +7443,7 @@
         <v>48</v>
       </c>
       <c r="D248" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>49</v>
@@ -7460,7 +7460,7 @@
         <v>48</v>
       </c>
       <c r="D249" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>49</v>
@@ -7477,7 +7477,7 @@
         <v>48</v>
       </c>
       <c r="D250" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>49</v>
@@ -7494,7 +7494,7 @@
         <v>48</v>
       </c>
       <c r="D251" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>49</v>
@@ -7511,7 +7511,7 @@
         <v>48</v>
       </c>
       <c r="D252" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E252" s="2" t="s">
         <v>49</v>
@@ -7528,7 +7528,7 @@
         <v>48</v>
       </c>
       <c r="D253" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>49</v>
@@ -7545,7 +7545,7 @@
         <v>48</v>
       </c>
       <c r="D254" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>49</v>
@@ -7562,7 +7562,7 @@
         <v>48</v>
       </c>
       <c r="D255" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>49</v>
@@ -7579,7 +7579,7 @@
         <v>48</v>
       </c>
       <c r="D256" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>49</v>
@@ -7596,7 +7596,7 @@
         <v>48</v>
       </c>
       <c r="D257" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>49</v>
@@ -7613,7 +7613,7 @@
         <v>48</v>
       </c>
       <c r="D258" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>49</v>
@@ -7630,7 +7630,7 @@
         <v>48</v>
       </c>
       <c r="D259" s="2">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>49</v>
@@ -7647,7 +7647,7 @@
         <v>48</v>
       </c>
       <c r="D260" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>49</v>
@@ -7664,7 +7664,7 @@
         <v>48</v>
       </c>
       <c r="D261" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>49</v>
@@ -7681,7 +7681,7 @@
         <v>48</v>
       </c>
       <c r="D262" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>49</v>
@@ -7698,7 +7698,7 @@
         <v>48</v>
       </c>
       <c r="D263" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>49</v>
@@ -7715,7 +7715,7 @@
         <v>48</v>
       </c>
       <c r="D264" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>49</v>
@@ -7732,7 +7732,7 @@
         <v>48</v>
       </c>
       <c r="D265" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>49</v>
@@ -7749,7 +7749,7 @@
         <v>48</v>
       </c>
       <c r="D266" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>49</v>
@@ -7766,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="D267" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>49</v>
@@ -7783,7 +7783,7 @@
         <v>48</v>
       </c>
       <c r="D268" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>49</v>
@@ -7800,7 +7800,7 @@
         <v>48</v>
       </c>
       <c r="D269" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>49</v>
@@ -7817,7 +7817,7 @@
         <v>48</v>
       </c>
       <c r="D270" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>49</v>
@@ -7834,7 +7834,7 @@
         <v>48</v>
       </c>
       <c r="D271" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>49</v>
@@ -7851,7 +7851,7 @@
         <v>48</v>
       </c>
       <c r="D272" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>49</v>
@@ -7868,7 +7868,7 @@
         <v>48</v>
       </c>
       <c r="D273" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>49</v>
@@ -7885,7 +7885,7 @@
         <v>48</v>
       </c>
       <c r="D274" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>49</v>
@@ -7902,7 +7902,7 @@
         <v>48</v>
       </c>
       <c r="D275" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>49</v>
@@ -7919,7 +7919,7 @@
         <v>48</v>
       </c>
       <c r="D276" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>49</v>
@@ -7936,7 +7936,7 @@
         <v>48</v>
       </c>
       <c r="D277" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>49</v>
@@ -7953,7 +7953,7 @@
         <v>48</v>
       </c>
       <c r="D278" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>49</v>
@@ -7970,7 +7970,7 @@
         <v>48</v>
       </c>
       <c r="D279" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>49</v>
@@ -7987,7 +7987,7 @@
         <v>48</v>
       </c>
       <c r="D280" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>49</v>
@@ -8038,7 +8038,7 @@
         <v>48</v>
       </c>
       <c r="D283" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>49</v>
@@ -8055,7 +8055,7 @@
         <v>48</v>
       </c>
       <c r="D284" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>49</v>
@@ -8072,7 +8072,7 @@
         <v>48</v>
       </c>
       <c r="D285" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>49</v>
@@ -8089,7 +8089,7 @@
         <v>48</v>
       </c>
       <c r="D286" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>49</v>
@@ -8106,7 +8106,7 @@
         <v>48</v>
       </c>
       <c r="D287" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>49</v>
@@ -8123,7 +8123,7 @@
         <v>48</v>
       </c>
       <c r="D288" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>49</v>
@@ -8140,7 +8140,7 @@
         <v>48</v>
       </c>
       <c r="D289" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>49</v>
@@ -8157,7 +8157,7 @@
         <v>48</v>
       </c>
       <c r="D290" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>49</v>
@@ -8174,7 +8174,7 @@
         <v>48</v>
       </c>
       <c r="D291" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>49</v>
@@ -8191,7 +8191,7 @@
         <v>48</v>
       </c>
       <c r="D292" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>49</v>
@@ -8208,7 +8208,7 @@
         <v>48</v>
       </c>
       <c r="D293" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>49</v>
@@ -8225,7 +8225,7 @@
         <v>48</v>
       </c>
       <c r="D294" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E294" s="2" t="s">
         <v>49</v>
@@ -8242,7 +8242,7 @@
         <v>48</v>
       </c>
       <c r="D295" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>49</v>
@@ -8259,7 +8259,7 @@
         <v>48</v>
       </c>
       <c r="D296" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>49</v>
@@ -8276,7 +8276,7 @@
         <v>48</v>
       </c>
       <c r="D297" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>49</v>
@@ -8293,7 +8293,7 @@
         <v>48</v>
       </c>
       <c r="D298" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>49</v>
@@ -8310,7 +8310,7 @@
         <v>48</v>
       </c>
       <c r="D299" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>49</v>
@@ -8327,7 +8327,7 @@
         <v>48</v>
       </c>
       <c r="D300" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>49</v>
@@ -8344,7 +8344,7 @@
         <v>48</v>
       </c>
       <c r="D301" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>49</v>
@@ -8361,7 +8361,7 @@
         <v>48</v>
       </c>
       <c r="D302" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>49</v>
@@ -8378,7 +8378,7 @@
         <v>48</v>
       </c>
       <c r="D303" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>49</v>
@@ -8395,7 +8395,7 @@
         <v>48</v>
       </c>
       <c r="D304" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>49</v>
@@ -8412,7 +8412,7 @@
         <v>48</v>
       </c>
       <c r="D305" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>49</v>
@@ -8429,7 +8429,7 @@
         <v>48</v>
       </c>
       <c r="D306" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>49</v>
@@ -8446,7 +8446,7 @@
         <v>48</v>
       </c>
       <c r="D307" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>49</v>
@@ -8463,7 +8463,7 @@
         <v>48</v>
       </c>
       <c r="D308" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>49</v>
@@ -8480,7 +8480,7 @@
         <v>48</v>
       </c>
       <c r="D309" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E309" s="2" t="s">
         <v>49</v>
@@ -8497,7 +8497,7 @@
         <v>48</v>
       </c>
       <c r="D310" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E310" s="2" t="s">
         <v>49</v>
@@ -8514,7 +8514,7 @@
         <v>48</v>
       </c>
       <c r="D311" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>49</v>
@@ -8531,7 +8531,7 @@
         <v>48</v>
       </c>
       <c r="D312" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>49</v>
@@ -8548,7 +8548,7 @@
         <v>48</v>
       </c>
       <c r="D313" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>49</v>
@@ -8565,7 +8565,7 @@
         <v>48</v>
       </c>
       <c r="D314" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>49</v>
@@ -8599,7 +8599,7 @@
         <v>48</v>
       </c>
       <c r="D316" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>49</v>
@@ -8633,7 +8633,7 @@
         <v>48</v>
       </c>
       <c r="D318" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>49</v>
@@ -8650,7 +8650,7 @@
         <v>48</v>
       </c>
       <c r="D319" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>49</v>
@@ -8667,7 +8667,7 @@
         <v>48</v>
       </c>
       <c r="D320" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>49</v>
@@ -8684,7 +8684,7 @@
         <v>48</v>
       </c>
       <c r="D321" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E321" s="2" t="s">
         <v>49</v>
@@ -8701,7 +8701,7 @@
         <v>48</v>
       </c>
       <c r="D322" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>49</v>
@@ -8718,7 +8718,7 @@
         <v>48</v>
       </c>
       <c r="D323" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>49</v>
@@ -8735,7 +8735,7 @@
         <v>48</v>
       </c>
       <c r="D324" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E324" s="2" t="s">
         <v>49</v>
@@ -8752,7 +8752,7 @@
         <v>48</v>
       </c>
       <c r="D325" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>49</v>
@@ -8769,7 +8769,7 @@
         <v>48</v>
       </c>
       <c r="D326" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>49</v>
@@ -8803,7 +8803,7 @@
         <v>48</v>
       </c>
       <c r="D328" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>49</v>
@@ -8820,7 +8820,7 @@
         <v>48</v>
       </c>
       <c r="D329" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>49</v>
@@ -8837,7 +8837,7 @@
         <v>48</v>
       </c>
       <c r="D330" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>49</v>
@@ -8854,7 +8854,7 @@
         <v>48</v>
       </c>
       <c r="D331" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>49</v>
@@ -8871,7 +8871,7 @@
         <v>48</v>
       </c>
       <c r="D332" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>49</v>
@@ -8888,7 +8888,7 @@
         <v>48</v>
       </c>
       <c r="D333" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>49</v>
@@ -8905,7 +8905,7 @@
         <v>48</v>
       </c>
       <c r="D334" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>49</v>
@@ -8922,7 +8922,7 @@
         <v>48</v>
       </c>
       <c r="D335" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E335" s="2" t="s">
         <v>49</v>
@@ -8939,7 +8939,7 @@
         <v>48</v>
       </c>
       <c r="D336" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E336" s="2" t="s">
         <v>49</v>
@@ -8956,7 +8956,7 @@
         <v>48</v>
       </c>
       <c r="D337" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>49</v>
@@ -8973,7 +8973,7 @@
         <v>48</v>
       </c>
       <c r="D338" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>49</v>
@@ -8990,7 +8990,7 @@
         <v>48</v>
       </c>
       <c r="D339" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>49</v>
@@ -9007,7 +9007,7 @@
         <v>48</v>
       </c>
       <c r="D340" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>49</v>
@@ -9024,7 +9024,7 @@
         <v>48</v>
       </c>
       <c r="D341" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>49</v>
@@ -9041,7 +9041,7 @@
         <v>48</v>
       </c>
       <c r="D342" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>49</v>
@@ -9058,7 +9058,7 @@
         <v>48</v>
       </c>
       <c r="D343" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>49</v>
@@ -9075,7 +9075,7 @@
         <v>48</v>
       </c>
       <c r="D344" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>49</v>
@@ -9092,7 +9092,7 @@
         <v>48</v>
       </c>
       <c r="D345" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>49</v>
@@ -9109,7 +9109,7 @@
         <v>48</v>
       </c>
       <c r="D346" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>49</v>
@@ -9126,7 +9126,7 @@
         <v>48</v>
       </c>
       <c r="D347" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>49</v>
@@ -9143,7 +9143,7 @@
         <v>48</v>
       </c>
       <c r="D348" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>49</v>
@@ -9160,7 +9160,7 @@
         <v>48</v>
       </c>
       <c r="D349" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>49</v>
@@ -9177,7 +9177,7 @@
         <v>48</v>
       </c>
       <c r="D350" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>49</v>
@@ -9194,7 +9194,7 @@
         <v>48</v>
       </c>
       <c r="D351" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>49</v>
@@ -9211,7 +9211,7 @@
         <v>48</v>
       </c>
       <c r="D352" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>49</v>
@@ -9228,7 +9228,7 @@
         <v>48</v>
       </c>
       <c r="D353" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>49</v>
@@ -9245,7 +9245,7 @@
         <v>48</v>
       </c>
       <c r="D354" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>49</v>
@@ -9262,7 +9262,7 @@
         <v>48</v>
       </c>
       <c r="D355" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>49</v>
@@ -9279,7 +9279,7 @@
         <v>48</v>
       </c>
       <c r="D356" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>49</v>
@@ -9296,7 +9296,7 @@
         <v>48</v>
       </c>
       <c r="D357" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>49</v>
@@ -9313,7 +9313,7 @@
         <v>48</v>
       </c>
       <c r="D358" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>49</v>
@@ -9330,7 +9330,7 @@
         <v>48</v>
       </c>
       <c r="D359" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>49</v>
@@ -9347,7 +9347,7 @@
         <v>48</v>
       </c>
       <c r="D360" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>49</v>
@@ -9364,7 +9364,7 @@
         <v>48</v>
       </c>
       <c r="D361" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>49</v>
@@ -9381,7 +9381,7 @@
         <v>48</v>
       </c>
       <c r="D362" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>49</v>
@@ -9398,7 +9398,7 @@
         <v>48</v>
       </c>
       <c r="D363" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>49</v>
@@ -9415,7 +9415,7 @@
         <v>48</v>
       </c>
       <c r="D364" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>49</v>
@@ -9432,7 +9432,7 @@
         <v>48</v>
       </c>
       <c r="D365" s="2">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>49</v>
@@ -9449,7 +9449,7 @@
         <v>48</v>
       </c>
       <c r="D366" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>49</v>
@@ -9466,7 +9466,7 @@
         <v>48</v>
       </c>
       <c r="D367" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>49</v>
@@ -9483,7 +9483,7 @@
         <v>48</v>
       </c>
       <c r="D368" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>49</v>
@@ -9500,7 +9500,7 @@
         <v>48</v>
       </c>
       <c r="D369" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>49</v>
@@ -9517,7 +9517,7 @@
         <v>48</v>
       </c>
       <c r="D370" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>49</v>
@@ -9534,7 +9534,7 @@
         <v>48</v>
       </c>
       <c r="D371" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>49</v>
@@ -9551,7 +9551,7 @@
         <v>48</v>
       </c>
       <c r="D372" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E372" s="2" t="s">
         <v>49</v>
@@ -9568,7 +9568,7 @@
         <v>48</v>
       </c>
       <c r="D373" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>49</v>
@@ -9585,7 +9585,7 @@
         <v>48</v>
       </c>
       <c r="D374" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>49</v>
@@ -9602,7 +9602,7 @@
         <v>48</v>
       </c>
       <c r="D375" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>49</v>
@@ -9619,7 +9619,7 @@
         <v>48</v>
       </c>
       <c r="D376" s="2">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>49</v>
@@ -9636,7 +9636,7 @@
         <v>48</v>
       </c>
       <c r="D377" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>49</v>
@@ -9653,7 +9653,7 @@
         <v>48</v>
       </c>
       <c r="D378" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>49</v>
@@ -9670,7 +9670,7 @@
         <v>48</v>
       </c>
       <c r="D379" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>49</v>
@@ -9687,7 +9687,7 @@
         <v>48</v>
       </c>
       <c r="D380" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>49</v>
@@ -9704,7 +9704,7 @@
         <v>48</v>
       </c>
       <c r="D381" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>49</v>
@@ -9721,7 +9721,7 @@
         <v>48</v>
       </c>
       <c r="D382" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>49</v>
@@ -9738,7 +9738,7 @@
         <v>48</v>
       </c>
       <c r="D383" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>49</v>
@@ -9755,7 +9755,7 @@
         <v>48</v>
       </c>
       <c r="D384" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>49</v>
@@ -9789,7 +9789,7 @@
         <v>48</v>
       </c>
       <c r="D386" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>49</v>
@@ -9806,7 +9806,7 @@
         <v>48</v>
       </c>
       <c r="D387" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>49</v>
@@ -9840,7 +9840,7 @@
         <v>48</v>
       </c>
       <c r="D389" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>49</v>
@@ -9857,7 +9857,7 @@
         <v>48</v>
       </c>
       <c r="D390" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E390" s="2" t="s">
         <v>49</v>
@@ -9874,7 +9874,7 @@
         <v>48</v>
       </c>
       <c r="D391" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>49</v>
@@ -9891,7 +9891,7 @@
         <v>48</v>
       </c>
       <c r="D392" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>49</v>
@@ -9908,7 +9908,7 @@
         <v>48</v>
       </c>
       <c r="D393" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>49</v>
@@ -9925,7 +9925,7 @@
         <v>48</v>
       </c>
       <c r="D394" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>49</v>
@@ -9942,7 +9942,7 @@
         <v>48</v>
       </c>
       <c r="D395" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>49</v>
@@ -9959,7 +9959,7 @@
         <v>48</v>
       </c>
       <c r="D396" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>49</v>
@@ -9976,7 +9976,7 @@
         <v>48</v>
       </c>
       <c r="D397" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>49</v>
@@ -9993,7 +9993,7 @@
         <v>48</v>
       </c>
       <c r="D398" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>49</v>
@@ -10010,7 +10010,7 @@
         <v>48</v>
       </c>
       <c r="D399" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E399" s="2" t="s">
         <v>49</v>
@@ -10027,7 +10027,7 @@
         <v>48</v>
       </c>
       <c r="D400" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E400" s="2" t="s">
         <v>49</v>
@@ -10044,7 +10044,7 @@
         <v>48</v>
       </c>
       <c r="D401" s="2">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>49</v>
@@ -10078,7 +10078,7 @@
         <v>48</v>
       </c>
       <c r="D403" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>49</v>
@@ -10095,7 +10095,7 @@
         <v>48</v>
       </c>
       <c r="D404" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>49</v>
@@ -10112,7 +10112,7 @@
         <v>48</v>
       </c>
       <c r="D405" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>49</v>
@@ -10129,7 +10129,7 @@
         <v>48</v>
       </c>
       <c r="D406" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>49</v>
@@ -10146,7 +10146,7 @@
         <v>48</v>
       </c>
       <c r="D407" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>49</v>
@@ -10163,7 +10163,7 @@
         <v>48</v>
       </c>
       <c r="D408" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>49</v>
@@ -10180,7 +10180,7 @@
         <v>48</v>
       </c>
       <c r="D409" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>49</v>
@@ -10197,7 +10197,7 @@
         <v>48</v>
       </c>
       <c r="D410" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>49</v>
@@ -10214,7 +10214,7 @@
         <v>48</v>
       </c>
       <c r="D411" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>49</v>
@@ -10231,7 +10231,7 @@
         <v>48</v>
       </c>
       <c r="D412" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>49</v>
@@ -10248,7 +10248,7 @@
         <v>48</v>
       </c>
       <c r="D413" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>49</v>
@@ -10265,7 +10265,7 @@
         <v>48</v>
       </c>
       <c r="D414" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>49</v>
@@ -10282,7 +10282,7 @@
         <v>48</v>
       </c>
       <c r="D415" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>49</v>
@@ -10299,7 +10299,7 @@
         <v>48</v>
       </c>
       <c r="D416" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>49</v>
@@ -10316,7 +10316,7 @@
         <v>48</v>
       </c>
       <c r="D417" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>49</v>
@@ -10333,7 +10333,7 @@
         <v>48</v>
       </c>
       <c r="D418" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>49</v>
@@ -10350,7 +10350,7 @@
         <v>48</v>
       </c>
       <c r="D419" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>49</v>
@@ -10367,7 +10367,7 @@
         <v>48</v>
       </c>
       <c r="D420" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>49</v>
@@ -10384,7 +10384,7 @@
         <v>48</v>
       </c>
       <c r="D421" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>49</v>
@@ -10401,7 +10401,7 @@
         <v>48</v>
       </c>
       <c r="D422" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>49</v>
@@ -10418,7 +10418,7 @@
         <v>48</v>
       </c>
       <c r="D423" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>49</v>
@@ -10435,7 +10435,7 @@
         <v>48</v>
       </c>
       <c r="D424" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>49</v>
@@ -10469,7 +10469,7 @@
         <v>48</v>
       </c>
       <c r="D426" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>49</v>
@@ -10486,7 +10486,7 @@
         <v>48</v>
       </c>
       <c r="D427" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E427" s="2" t="s">
         <v>49</v>
@@ -10503,7 +10503,7 @@
         <v>48</v>
       </c>
       <c r="D428" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>49</v>
@@ -10520,7 +10520,7 @@
         <v>48</v>
       </c>
       <c r="D429" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>49</v>
@@ -10537,7 +10537,7 @@
         <v>48</v>
       </c>
       <c r="D430" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>49</v>
@@ -10554,7 +10554,7 @@
         <v>48</v>
       </c>
       <c r="D431" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>49</v>
@@ -10571,7 +10571,7 @@
         <v>48</v>
       </c>
       <c r="D432" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>49</v>
@@ -10588,7 +10588,7 @@
         <v>48</v>
       </c>
       <c r="D433" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>49</v>
@@ -10605,7 +10605,7 @@
         <v>48</v>
       </c>
       <c r="D434" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>49</v>
@@ -10622,7 +10622,7 @@
         <v>48</v>
       </c>
       <c r="D435" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>49</v>
@@ -10656,7 +10656,7 @@
         <v>48</v>
       </c>
       <c r="D437" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>49</v>
@@ -10673,7 +10673,7 @@
         <v>48</v>
       </c>
       <c r="D438" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>49</v>
@@ -10690,7 +10690,7 @@
         <v>48</v>
       </c>
       <c r="D439" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>49</v>
@@ -10707,7 +10707,7 @@
         <v>48</v>
       </c>
       <c r="D440" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>49</v>
@@ -10724,7 +10724,7 @@
         <v>48</v>
       </c>
       <c r="D441" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>49</v>
@@ -10758,7 +10758,7 @@
         <v>48</v>
       </c>
       <c r="D443" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>49</v>
@@ -10775,7 +10775,7 @@
         <v>48</v>
       </c>
       <c r="D444" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>49</v>
@@ -10792,7 +10792,7 @@
         <v>48</v>
       </c>
       <c r="D445" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>49</v>
@@ -10809,7 +10809,7 @@
         <v>48</v>
       </c>
       <c r="D446" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>49</v>
@@ -10826,7 +10826,7 @@
         <v>48</v>
       </c>
       <c r="D447" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>49</v>
@@ -10843,7 +10843,7 @@
         <v>48</v>
       </c>
       <c r="D448" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E448" s="2" t="s">
         <v>49</v>
@@ -10860,7 +10860,7 @@
         <v>48</v>
       </c>
       <c r="D449" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>49</v>
@@ -10877,7 +10877,7 @@
         <v>48</v>
       </c>
       <c r="D450" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E450" s="2" t="s">
         <v>49</v>
@@ -10894,7 +10894,7 @@
         <v>48</v>
       </c>
       <c r="D451" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>49</v>
@@ -10911,7 +10911,7 @@
         <v>48</v>
       </c>
       <c r="D452" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>49</v>
@@ -10928,7 +10928,7 @@
         <v>48</v>
       </c>
       <c r="D453" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>49</v>
@@ -10945,7 +10945,7 @@
         <v>48</v>
       </c>
       <c r="D454" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>49</v>
@@ -10979,7 +10979,7 @@
         <v>48</v>
       </c>
       <c r="D456" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>49</v>
@@ -10996,7 +10996,7 @@
         <v>48</v>
       </c>
       <c r="D457" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>49</v>
@@ -11013,7 +11013,7 @@
         <v>48</v>
       </c>
       <c r="D458" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>49</v>
@@ -11030,7 +11030,7 @@
         <v>48</v>
       </c>
       <c r="D459" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>49</v>
@@ -11047,7 +11047,7 @@
         <v>48</v>
       </c>
       <c r="D460" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>49</v>
@@ -11064,7 +11064,7 @@
         <v>48</v>
       </c>
       <c r="D461" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>49</v>
@@ -11081,7 +11081,7 @@
         <v>48</v>
       </c>
       <c r="D462" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>49</v>
@@ -11098,7 +11098,7 @@
         <v>48</v>
       </c>
       <c r="D463" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>49</v>
@@ -11115,7 +11115,7 @@
         <v>48</v>
       </c>
       <c r="D464" s="2">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>49</v>
@@ -11132,7 +11132,7 @@
         <v>48</v>
       </c>
       <c r="D465" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>49</v>
@@ -11149,7 +11149,7 @@
         <v>48</v>
       </c>
       <c r="D466" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>49</v>
@@ -11166,7 +11166,7 @@
         <v>48</v>
       </c>
       <c r="D467" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>49</v>
@@ -11183,7 +11183,7 @@
         <v>48</v>
       </c>
       <c r="D468" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>49</v>
@@ -11200,7 +11200,7 @@
         <v>48</v>
       </c>
       <c r="D469" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>49</v>
@@ -11217,7 +11217,7 @@
         <v>48</v>
       </c>
       <c r="D470" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E470" s="2" t="s">
         <v>49</v>
@@ -11234,7 +11234,7 @@
         <v>48</v>
       </c>
       <c r="D471" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>49</v>
@@ -11251,7 +11251,7 @@
         <v>48</v>
       </c>
       <c r="D472" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>49</v>
@@ -11268,7 +11268,7 @@
         <v>48</v>
       </c>
       <c r="D473" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>49</v>
@@ -11285,7 +11285,7 @@
         <v>48</v>
       </c>
       <c r="D474" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E474" s="2" t="s">
         <v>49</v>
@@ -11302,7 +11302,7 @@
         <v>48</v>
       </c>
       <c r="D475" s="2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>49</v>
@@ -11319,7 +11319,7 @@
         <v>48</v>
       </c>
       <c r="D476" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>49</v>
@@ -11336,7 +11336,7 @@
         <v>48</v>
       </c>
       <c r="D477" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>49</v>
@@ -11353,7 +11353,7 @@
         <v>48</v>
       </c>
       <c r="D478" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>49</v>
@@ -11370,7 +11370,7 @@
         <v>48</v>
       </c>
       <c r="D479" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>49</v>
@@ -11387,7 +11387,7 @@
         <v>48</v>
       </c>
       <c r="D480" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>49</v>
@@ -11404,7 +11404,7 @@
         <v>48</v>
       </c>
       <c r="D481" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>49</v>
@@ -11421,7 +11421,7 @@
         <v>48</v>
       </c>
       <c r="D482" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>49</v>
@@ -11438,7 +11438,7 @@
         <v>48</v>
       </c>
       <c r="D483" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>49</v>
@@ -11472,7 +11472,7 @@
         <v>48</v>
       </c>
       <c r="D485" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>49</v>
@@ -11489,7 +11489,7 @@
         <v>48</v>
       </c>
       <c r="D486" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>49</v>
@@ -11506,7 +11506,7 @@
         <v>48</v>
       </c>
       <c r="D487" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>49</v>
@@ -11523,7 +11523,7 @@
         <v>48</v>
       </c>
       <c r="D488" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>49</v>
@@ -11540,7 +11540,7 @@
         <v>48</v>
       </c>
       <c r="D489" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>49</v>
@@ -11557,7 +11557,7 @@
         <v>48</v>
       </c>
       <c r="D490" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>49</v>
@@ -11574,7 +11574,7 @@
         <v>48</v>
       </c>
       <c r="D491" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>49</v>
@@ -11591,7 +11591,7 @@
         <v>48</v>
       </c>
       <c r="D492" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>49</v>
@@ -11608,7 +11608,7 @@
         <v>48</v>
       </c>
       <c r="D493" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>49</v>
@@ -11625,7 +11625,7 @@
         <v>48</v>
       </c>
       <c r="D494" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>49</v>
@@ -11642,7 +11642,7 @@
         <v>48</v>
       </c>
       <c r="D495" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>49</v>
@@ -11659,7 +11659,7 @@
         <v>48</v>
       </c>
       <c r="D496" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E496" s="2" t="s">
         <v>49</v>
@@ -11676,7 +11676,7 @@
         <v>48</v>
       </c>
       <c r="D497" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>49</v>
@@ -11710,7 +11710,7 @@
         <v>48</v>
       </c>
       <c r="D499" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>49</v>
@@ -11727,7 +11727,7 @@
         <v>48</v>
       </c>
       <c r="D500" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>49</v>
@@ -11744,7 +11744,7 @@
         <v>48</v>
       </c>
       <c r="D501" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>49</v>
@@ -11761,7 +11761,7 @@
         <v>48</v>
       </c>
       <c r="D502" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>49</v>
@@ -11778,7 +11778,7 @@
         <v>48</v>
       </c>
       <c r="D503" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>49</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="D504" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>49</v>
@@ -11812,7 +11812,7 @@
         <v>48</v>
       </c>
       <c r="D505" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E505" s="2" t="s">
         <v>49</v>
@@ -11829,7 +11829,7 @@
         <v>48</v>
       </c>
       <c r="D506" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>49</v>
@@ -11846,7 +11846,7 @@
         <v>48</v>
       </c>
       <c r="D507" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>49</v>
@@ -11863,7 +11863,7 @@
         <v>48</v>
       </c>
       <c r="D508" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>49</v>
@@ -11880,7 +11880,7 @@
         <v>48</v>
       </c>
       <c r="D509" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E509" s="2" t="s">
         <v>49</v>
@@ -11897,7 +11897,7 @@
         <v>48</v>
       </c>
       <c r="D510" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>49</v>
@@ -11914,7 +11914,7 @@
         <v>48</v>
       </c>
       <c r="D511" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>49</v>
@@ -11931,7 +11931,7 @@
         <v>48</v>
       </c>
       <c r="D512" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>49</v>
@@ -11948,7 +11948,7 @@
         <v>48</v>
       </c>
       <c r="D513" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>49</v>
@@ -11965,7 +11965,7 @@
         <v>48</v>
       </c>
       <c r="D514" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>49</v>
@@ -11982,7 +11982,7 @@
         <v>48</v>
       </c>
       <c r="D515" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>49</v>
@@ -11999,7 +11999,7 @@
         <v>48</v>
       </c>
       <c r="D516" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>49</v>
@@ -12016,7 +12016,7 @@
         <v>48</v>
       </c>
       <c r="D517" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E517" s="2" t="s">
         <v>49</v>
@@ -12033,7 +12033,7 @@
         <v>48</v>
       </c>
       <c r="D518" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>49</v>
@@ -12050,7 +12050,7 @@
         <v>48</v>
       </c>
       <c r="D519" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>49</v>
@@ -12084,7 +12084,7 @@
         <v>48</v>
       </c>
       <c r="D521" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>49</v>
@@ -12101,7 +12101,7 @@
         <v>48</v>
       </c>
       <c r="D522" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>49</v>
@@ -12118,7 +12118,7 @@
         <v>48</v>
       </c>
       <c r="D523" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>49</v>
@@ -12135,7 +12135,7 @@
         <v>48</v>
       </c>
       <c r="D524" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>49</v>
@@ -12152,7 +12152,7 @@
         <v>48</v>
       </c>
       <c r="D525" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>49</v>
@@ -12169,7 +12169,7 @@
         <v>48</v>
       </c>
       <c r="D526" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>49</v>
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="D527" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>49</v>
@@ -12203,7 +12203,7 @@
         <v>48</v>
       </c>
       <c r="D528" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>49</v>
@@ -12220,7 +12220,7 @@
         <v>48</v>
       </c>
       <c r="D529" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>49</v>
@@ -12237,7 +12237,7 @@
         <v>48</v>
       </c>
       <c r="D530" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>49</v>
@@ -12254,7 +12254,7 @@
         <v>48</v>
       </c>
       <c r="D531" s="2">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>49</v>
@@ -12271,7 +12271,7 @@
         <v>48</v>
       </c>
       <c r="D532" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>49</v>
@@ -12288,7 +12288,7 @@
         <v>48</v>
       </c>
       <c r="D533" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>49</v>
@@ -12305,7 +12305,7 @@
         <v>48</v>
       </c>
       <c r="D534" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>49</v>
@@ -12339,7 +12339,7 @@
         <v>48</v>
       </c>
       <c r="D536" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>49</v>
@@ -12356,7 +12356,7 @@
         <v>48</v>
       </c>
       <c r="D537" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>49</v>
@@ -12373,7 +12373,7 @@
         <v>48</v>
       </c>
       <c r="D538" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>49</v>
@@ -12390,7 +12390,7 @@
         <v>48</v>
       </c>
       <c r="D539" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>49</v>
@@ -12407,7 +12407,7 @@
         <v>48</v>
       </c>
       <c r="D540" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>49</v>
@@ -12424,7 +12424,7 @@
         <v>48</v>
       </c>
       <c r="D541" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>49</v>
@@ -12441,7 +12441,7 @@
         <v>48</v>
       </c>
       <c r="D542" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>49</v>
@@ -12458,7 +12458,7 @@
         <v>48</v>
       </c>
       <c r="D543" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>49</v>
@@ -12475,7 +12475,7 @@
         <v>48</v>
       </c>
       <c r="D544" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>49</v>
@@ -12509,7 +12509,7 @@
         <v>48</v>
       </c>
       <c r="D546" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>49</v>
@@ -12526,7 +12526,7 @@
         <v>48</v>
       </c>
       <c r="D547" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>49</v>
@@ -12543,7 +12543,7 @@
         <v>48</v>
       </c>
       <c r="D548" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>49</v>
@@ -12560,7 +12560,7 @@
         <v>48</v>
       </c>
       <c r="D549" s="2">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>49</v>
@@ -12577,7 +12577,7 @@
         <v>48</v>
       </c>
       <c r="D550" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>49</v>
@@ -12594,7 +12594,7 @@
         <v>48</v>
       </c>
       <c r="D551" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E551" s="2" t="s">
         <v>49</v>
@@ -12611,7 +12611,7 @@
         <v>48</v>
       </c>
       <c r="D552" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>49</v>
@@ -12628,7 +12628,7 @@
         <v>48</v>
       </c>
       <c r="D553" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>49</v>
@@ -12645,7 +12645,7 @@
         <v>48</v>
       </c>
       <c r="D554" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>49</v>
@@ -12662,7 +12662,7 @@
         <v>48</v>
       </c>
       <c r="D555" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>49</v>
@@ -12679,7 +12679,7 @@
         <v>48</v>
       </c>
       <c r="D556" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>49</v>
@@ -12696,7 +12696,7 @@
         <v>48</v>
       </c>
       <c r="D557" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>49</v>
@@ -12713,7 +12713,7 @@
         <v>48</v>
       </c>
       <c r="D558" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E558" s="2" t="s">
         <v>49</v>
@@ -12730,7 +12730,7 @@
         <v>48</v>
       </c>
       <c r="D559" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>49</v>
@@ -12747,7 +12747,7 @@
         <v>48</v>
       </c>
       <c r="D560" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>49</v>
@@ -12764,7 +12764,7 @@
         <v>48</v>
       </c>
       <c r="D561" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>49</v>
@@ -12781,7 +12781,7 @@
         <v>48</v>
       </c>
       <c r="D562" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>49</v>
@@ -12798,7 +12798,7 @@
         <v>48</v>
       </c>
       <c r="D563" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>49</v>
@@ -12815,7 +12815,7 @@
         <v>48</v>
       </c>
       <c r="D564" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>49</v>
@@ -12832,7 +12832,7 @@
         <v>48</v>
       </c>
       <c r="D565" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>49</v>
@@ -12849,7 +12849,7 @@
         <v>48</v>
       </c>
       <c r="D566" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>49</v>
@@ -12866,7 +12866,7 @@
         <v>48</v>
       </c>
       <c r="D567" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>49</v>
@@ -12883,7 +12883,7 @@
         <v>48</v>
       </c>
       <c r="D568" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>49</v>
@@ -12900,7 +12900,7 @@
         <v>48</v>
       </c>
       <c r="D569" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>49</v>
@@ -12917,7 +12917,7 @@
         <v>48</v>
       </c>
       <c r="D570" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>49</v>
@@ -12934,7 +12934,7 @@
         <v>48</v>
       </c>
       <c r="D571" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>49</v>
@@ -12951,7 +12951,7 @@
         <v>48</v>
       </c>
       <c r="D572" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E572" s="2" t="s">
         <v>49</v>
@@ -12968,7 +12968,7 @@
         <v>48</v>
       </c>
       <c r="D573" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>49</v>
@@ -12985,7 +12985,7 @@
         <v>48</v>
       </c>
       <c r="D574" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>49</v>
@@ -13002,7 +13002,7 @@
         <v>48</v>
       </c>
       <c r="D575" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>49</v>
@@ -13019,7 +13019,7 @@
         <v>48</v>
       </c>
       <c r="D576" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>49</v>
@@ -13053,7 +13053,7 @@
         <v>48</v>
       </c>
       <c r="D578" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E578" s="2" t="s">
         <v>49</v>
@@ -13070,7 +13070,7 @@
         <v>48</v>
       </c>
       <c r="D579" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E579" s="2" t="s">
         <v>49</v>
@@ -13087,7 +13087,7 @@
         <v>48</v>
       </c>
       <c r="D580" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>49</v>
@@ -13104,7 +13104,7 @@
         <v>48</v>
       </c>
       <c r="D581" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>49</v>
@@ -13121,7 +13121,7 @@
         <v>48</v>
       </c>
       <c r="D582" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E582" s="2" t="s">
         <v>49</v>
@@ -13138,7 +13138,7 @@
         <v>48</v>
       </c>
       <c r="D583" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>49</v>
@@ -13155,7 +13155,7 @@
         <v>48</v>
       </c>
       <c r="D584" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>49</v>
@@ -13172,7 +13172,7 @@
         <v>48</v>
       </c>
       <c r="D585" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E585" s="2" t="s">
         <v>49</v>
@@ -13189,7 +13189,7 @@
         <v>48</v>
       </c>
       <c r="D586" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E586" s="2" t="s">
         <v>49</v>
@@ -13206,7 +13206,7 @@
         <v>48</v>
       </c>
       <c r="D587" s="2">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>49</v>
@@ -13223,7 +13223,7 @@
         <v>48</v>
       </c>
       <c r="D588" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E588" s="2" t="s">
         <v>49</v>
@@ -13240,7 +13240,7 @@
         <v>48</v>
       </c>
       <c r="D589" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E589" s="2" t="s">
         <v>49</v>
@@ -13257,7 +13257,7 @@
         <v>48</v>
       </c>
       <c r="D590" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>49</v>
@@ -13274,7 +13274,7 @@
         <v>48</v>
       </c>
       <c r="D591" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>49</v>
@@ -13291,7 +13291,7 @@
         <v>48</v>
       </c>
       <c r="D592" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>49</v>
@@ -13325,7 +13325,7 @@
         <v>48</v>
       </c>
       <c r="D594" s="2">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E594" s="2" t="s">
         <v>49</v>
@@ -13342,7 +13342,7 @@
         <v>48</v>
       </c>
       <c r="D595" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>49</v>
@@ -13359,7 +13359,7 @@
         <v>48</v>
       </c>
       <c r="D596" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>49</v>
@@ -13376,7 +13376,7 @@
         <v>48</v>
       </c>
       <c r="D597" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>49</v>
@@ -13393,7 +13393,7 @@
         <v>48</v>
       </c>
       <c r="D598" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E598" s="2" t="s">
         <v>49</v>
@@ -13410,7 +13410,7 @@
         <v>48</v>
       </c>
       <c r="D599" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>49</v>
@@ -13444,7 +13444,7 @@
         <v>48</v>
       </c>
       <c r="D601" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E601" s="2" t="s">
         <v>49</v>
@@ -13461,7 +13461,7 @@
         <v>48</v>
       </c>
       <c r="D602" s="2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>49</v>
@@ -13478,7 +13478,7 @@
         <v>48</v>
       </c>
       <c r="D603" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>49</v>
@@ -13495,7 +13495,7 @@
         <v>48</v>
       </c>
       <c r="D604" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>49</v>
@@ -13512,7 +13512,7 @@
         <v>48</v>
       </c>
       <c r="D605" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>49</v>
@@ -13529,7 +13529,7 @@
         <v>48</v>
       </c>
       <c r="D606" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>49</v>
@@ -13546,7 +13546,7 @@
         <v>48</v>
       </c>
       <c r="D607" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>49</v>
@@ -13563,7 +13563,7 @@
         <v>48</v>
       </c>
       <c r="D608" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E608" s="2" t="s">
         <v>49</v>
@@ -13597,7 +13597,7 @@
         <v>48</v>
       </c>
       <c r="D610" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>49</v>
@@ -13614,7 +13614,7 @@
         <v>48</v>
       </c>
       <c r="D611" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>49</v>
@@ -13631,7 +13631,7 @@
         <v>48</v>
       </c>
       <c r="D612" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E612" s="2" t="s">
         <v>49</v>
@@ -13648,7 +13648,7 @@
         <v>48</v>
       </c>
       <c r="D613" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E613" s="2" t="s">
         <v>49</v>
@@ -13665,7 +13665,7 @@
         <v>48</v>
       </c>
       <c r="D614" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E614" s="2" t="s">
         <v>49</v>
@@ -13682,7 +13682,7 @@
         <v>48</v>
       </c>
       <c r="D615" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E615" s="2" t="s">
         <v>49</v>
@@ -13699,7 +13699,7 @@
         <v>48</v>
       </c>
       <c r="D616" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E616" s="2" t="s">
         <v>49</v>
@@ -13716,7 +13716,7 @@
         <v>48</v>
       </c>
       <c r="D617" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>49</v>
@@ -13733,7 +13733,7 @@
         <v>48</v>
       </c>
       <c r="D618" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E618" s="2" t="s">
         <v>49</v>
@@ -13750,7 +13750,7 @@
         <v>48</v>
       </c>
       <c r="D619" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E619" s="2" t="s">
         <v>49</v>
@@ -13767,7 +13767,7 @@
         <v>48</v>
       </c>
       <c r="D620" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E620" s="2" t="s">
         <v>49</v>
@@ -13784,7 +13784,7 @@
         <v>48</v>
       </c>
       <c r="D621" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E621" s="2" t="s">
         <v>49</v>
@@ -13801,7 +13801,7 @@
         <v>48</v>
       </c>
       <c r="D622" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E622" s="2" t="s">
         <v>49</v>
@@ -13818,7 +13818,7 @@
         <v>48</v>
       </c>
       <c r="D623" s="2">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E623" s="2" t="s">
         <v>49</v>
@@ -13835,7 +13835,7 @@
         <v>48</v>
       </c>
       <c r="D624" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E624" s="2" t="s">
         <v>49</v>
@@ -13852,7 +13852,7 @@
         <v>48</v>
       </c>
       <c r="D625" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>49</v>
@@ -13869,7 +13869,7 @@
         <v>48</v>
       </c>
       <c r="D626" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E626" s="2" t="s">
         <v>49</v>
@@ -13886,7 +13886,7 @@
         <v>48</v>
       </c>
       <c r="D627" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E627" s="2" t="s">
         <v>49</v>
@@ -13903,7 +13903,7 @@
         <v>48</v>
       </c>
       <c r="D628" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E628" s="2" t="s">
         <v>49</v>
@@ -13920,7 +13920,7 @@
         <v>48</v>
       </c>
       <c r="D629" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E629" s="2" t="s">
         <v>49</v>
@@ -13954,7 +13954,7 @@
         <v>48</v>
       </c>
       <c r="D631" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E631" s="2" t="s">
         <v>49</v>
@@ -13971,7 +13971,7 @@
         <v>48</v>
       </c>
       <c r="D632" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E632" s="2" t="s">
         <v>49</v>
@@ -13988,7 +13988,7 @@
         <v>48</v>
       </c>
       <c r="D633" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E633" s="2" t="s">
         <v>49</v>
@@ -14005,7 +14005,7 @@
         <v>48</v>
       </c>
       <c r="D634" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E634" s="2" t="s">
         <v>49</v>
@@ -14022,7 +14022,7 @@
         <v>48</v>
       </c>
       <c r="D635" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E635" s="2" t="s">
         <v>49</v>
@@ -14056,7 +14056,7 @@
         <v>48</v>
       </c>
       <c r="D637" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>49</v>
@@ -14073,7 +14073,7 @@
         <v>48</v>
       </c>
       <c r="D638" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E638" s="2" t="s">
         <v>49</v>
@@ -14090,7 +14090,7 @@
         <v>48</v>
       </c>
       <c r="D639" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E639" s="2" t="s">
         <v>49</v>
@@ -14107,7 +14107,7 @@
         <v>48</v>
       </c>
       <c r="D640" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E640" s="2" t="s">
         <v>49</v>
@@ -14124,7 +14124,7 @@
         <v>48</v>
       </c>
       <c r="D641" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>49</v>
@@ -14141,7 +14141,7 @@
         <v>48</v>
       </c>
       <c r="D642" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E642" s="2" t="s">
         <v>49</v>
@@ -14158,7 +14158,7 @@
         <v>48</v>
       </c>
       <c r="D643" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E643" s="2" t="s">
         <v>49</v>
@@ -14175,7 +14175,7 @@
         <v>48</v>
       </c>
       <c r="D644" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E644" s="2" t="s">
         <v>49</v>
@@ -14192,7 +14192,7 @@
         <v>48</v>
       </c>
       <c r="D645" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E645" s="2" t="s">
         <v>49</v>
@@ -14209,7 +14209,7 @@
         <v>48</v>
       </c>
       <c r="D646" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>49</v>
@@ -14226,7 +14226,7 @@
         <v>48</v>
       </c>
       <c r="D647" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>49</v>
@@ -14243,7 +14243,7 @@
         <v>48</v>
       </c>
       <c r="D648" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E648" s="2" t="s">
         <v>49</v>
@@ -14260,7 +14260,7 @@
         <v>48</v>
       </c>
       <c r="D649" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E649" s="2" t="s">
         <v>49</v>
@@ -14277,7 +14277,7 @@
         <v>48</v>
       </c>
       <c r="D650" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E650" s="2" t="s">
         <v>49</v>
@@ -14294,7 +14294,7 @@
         <v>48</v>
       </c>
       <c r="D651" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E651" s="2" t="s">
         <v>49</v>
@@ -14311,7 +14311,7 @@
         <v>48</v>
       </c>
       <c r="D652" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E652" s="2" t="s">
         <v>49</v>
@@ -14328,7 +14328,7 @@
         <v>48</v>
       </c>
       <c r="D653" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E653" s="2" t="s">
         <v>49</v>
@@ -14345,7 +14345,7 @@
         <v>48</v>
       </c>
       <c r="D654" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E654" s="2" t="s">
         <v>49</v>
@@ -14362,7 +14362,7 @@
         <v>48</v>
       </c>
       <c r="D655" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E655" s="2" t="s">
         <v>49</v>
@@ -14379,7 +14379,7 @@
         <v>48</v>
       </c>
       <c r="D656" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E656" s="2" t="s">
         <v>49</v>
@@ -14396,7 +14396,7 @@
         <v>48</v>
       </c>
       <c r="D657" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E657" s="2" t="s">
         <v>49</v>
@@ -14413,7 +14413,7 @@
         <v>48</v>
       </c>
       <c r="D658" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E658" s="2" t="s">
         <v>49</v>
@@ -14430,7 +14430,7 @@
         <v>48</v>
       </c>
       <c r="D659" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E659" s="2" t="s">
         <v>49</v>
@@ -14447,7 +14447,7 @@
         <v>48</v>
       </c>
       <c r="D660" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E660" s="2" t="s">
         <v>49</v>
@@ -14464,7 +14464,7 @@
         <v>48</v>
       </c>
       <c r="D661" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E661" s="2" t="s">
         <v>49</v>
@@ -14481,7 +14481,7 @@
         <v>48</v>
       </c>
       <c r="D662" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E662" s="2" t="s">
         <v>49</v>
@@ -14498,7 +14498,7 @@
         <v>48</v>
       </c>
       <c r="D663" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E663" s="2" t="s">
         <v>49</v>
@@ -14515,7 +14515,7 @@
         <v>48</v>
       </c>
       <c r="D664" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E664" s="2" t="s">
         <v>49</v>
@@ -14532,7 +14532,7 @@
         <v>48</v>
       </c>
       <c r="D665" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E665" s="2" t="s">
         <v>49</v>
@@ -14549,7 +14549,7 @@
         <v>48</v>
       </c>
       <c r="D666" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E666" s="2" t="s">
         <v>49</v>
@@ -14566,7 +14566,7 @@
         <v>48</v>
       </c>
       <c r="D667" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E667" s="2" t="s">
         <v>49</v>
@@ -14583,7 +14583,7 @@
         <v>48</v>
       </c>
       <c r="D668" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E668" s="2" t="s">
         <v>49</v>
@@ -14600,7 +14600,7 @@
         <v>48</v>
       </c>
       <c r="D669" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E669" s="2" t="s">
         <v>49</v>
@@ -14617,7 +14617,7 @@
         <v>48</v>
       </c>
       <c r="D670" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E670" s="2" t="s">
         <v>49</v>
@@ -14634,7 +14634,7 @@
         <v>48</v>
       </c>
       <c r="D671" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E671" s="2" t="s">
         <v>49</v>
@@ -14651,7 +14651,7 @@
         <v>48</v>
       </c>
       <c r="D672" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E672" s="2" t="s">
         <v>49</v>
@@ -14668,7 +14668,7 @@
         <v>48</v>
       </c>
       <c r="D673" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E673" s="2" t="s">
         <v>49</v>
@@ -14685,7 +14685,7 @@
         <v>48</v>
       </c>
       <c r="D674" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E674" s="2" t="s">
         <v>49</v>
@@ -14702,7 +14702,7 @@
         <v>48</v>
       </c>
       <c r="D675" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E675" s="2" t="s">
         <v>49</v>
@@ -14719,7 +14719,7 @@
         <v>48</v>
       </c>
       <c r="D676" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E676" s="2" t="s">
         <v>49</v>
@@ -14736,7 +14736,7 @@
         <v>48</v>
       </c>
       <c r="D677" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E677" s="2" t="s">
         <v>49</v>
@@ -14753,7 +14753,7 @@
         <v>48</v>
       </c>
       <c r="D678" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E678" s="2" t="s">
         <v>49</v>
@@ -14770,7 +14770,7 @@
         <v>48</v>
       </c>
       <c r="D679" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E679" s="2" t="s">
         <v>49</v>
@@ -14787,7 +14787,7 @@
         <v>48</v>
       </c>
       <c r="D680" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E680" s="2" t="s">
         <v>49</v>
@@ -14804,7 +14804,7 @@
         <v>48</v>
       </c>
       <c r="D681" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>49</v>
@@ -14821,7 +14821,7 @@
         <v>48</v>
       </c>
       <c r="D682" s="2">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="E682" s="2" t="s">
         <v>49</v>
@@ -14838,7 +14838,7 @@
         <v>48</v>
       </c>
       <c r="D683" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E683" s="2" t="s">
         <v>49</v>
@@ -14855,7 +14855,7 @@
         <v>48</v>
       </c>
       <c r="D684" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E684" s="2" t="s">
         <v>49</v>
@@ -14872,7 +14872,7 @@
         <v>48</v>
       </c>
       <c r="D685" s="2">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E685" s="2" t="s">
         <v>49</v>
@@ -14889,7 +14889,7 @@
         <v>48</v>
       </c>
       <c r="D686" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E686" s="2" t="s">
         <v>49</v>
@@ -14906,7 +14906,7 @@
         <v>48</v>
       </c>
       <c r="D687" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E687" s="2" t="s">
         <v>49</v>
@@ -14923,7 +14923,7 @@
         <v>48</v>
       </c>
       <c r="D688" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>49</v>
@@ -14940,7 +14940,7 @@
         <v>48</v>
       </c>
       <c r="D689" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E689" s="2" t="s">
         <v>49</v>
@@ -14957,7 +14957,7 @@
         <v>48</v>
       </c>
       <c r="D690" s="2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E690" s="2" t="s">
         <v>49</v>
@@ -14974,7 +14974,7 @@
         <v>48</v>
       </c>
       <c r="D691" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E691" s="2" t="s">
         <v>49</v>
@@ -14991,7 +14991,7 @@
         <v>48</v>
       </c>
       <c r="D692" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E692" s="2" t="s">
         <v>49</v>
@@ -15008,7 +15008,7 @@
         <v>48</v>
       </c>
       <c r="D693" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E693" s="2" t="s">
         <v>49</v>

--- a/reports/selenium/test-results.xlsx
+++ b/reports/selenium/test-results.xlsx
@@ -30,7 +30,7 @@
     <t>Execution Timestamp</t>
   </si>
   <si>
-    <t>7/27/2026, 8:35:34 AM</t>
+    <t>7/27/2026, 8:39:20 AM</t>
   </si>
   <si>
     <t>Total Tests Executed</t>
@@ -2721,7 +2721,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="2">
-        <v>8748</v>
+        <v>8885</v>
       </c>
     </row>
   </sheetData>
@@ -3261,7 +3261,7 @@
         <v>48</v>
       </c>
       <c r="D2" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>49</v>
@@ -3278,7 +3278,7 @@
         <v>48</v>
       </c>
       <c r="D3" s="2">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>49</v>
@@ -3295,7 +3295,7 @@
         <v>48</v>
       </c>
       <c r="D4" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>49</v>
@@ -3312,7 +3312,7 @@
         <v>48</v>
       </c>
       <c r="D5" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>49</v>
@@ -3329,7 +3329,7 @@
         <v>48</v>
       </c>
       <c r="D6" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>49</v>
@@ -3346,7 +3346,7 @@
         <v>48</v>
       </c>
       <c r="D7" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>49</v>
@@ -3380,7 +3380,7 @@
         <v>48</v>
       </c>
       <c r="D9" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>49</v>
@@ -3397,7 +3397,7 @@
         <v>48</v>
       </c>
       <c r="D10" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>49</v>
@@ -3414,7 +3414,7 @@
         <v>48</v>
       </c>
       <c r="D11" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>49</v>
@@ -3431,7 +3431,7 @@
         <v>48</v>
       </c>
       <c r="D12" s="2">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>49</v>
@@ -3448,7 +3448,7 @@
         <v>48</v>
       </c>
       <c r="D13" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>49</v>
@@ -3465,7 +3465,7 @@
         <v>48</v>
       </c>
       <c r="D14" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>49</v>
@@ -3482,7 +3482,7 @@
         <v>48</v>
       </c>
       <c r="D15" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>49</v>
@@ -3550,7 +3550,7 @@
         <v>48</v>
       </c>
       <c r="D19" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>49</v>
@@ -3567,7 +3567,7 @@
         <v>48</v>
       </c>
       <c r="D20" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>49</v>
@@ -3601,7 +3601,7 @@
         <v>48</v>
       </c>
       <c r="D22" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>49</v>
@@ -3618,7 +3618,7 @@
         <v>48</v>
       </c>
       <c r="D23" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>49</v>
@@ -3635,7 +3635,7 @@
         <v>48</v>
       </c>
       <c r="D24" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>49</v>
@@ -3652,7 +3652,7 @@
         <v>48</v>
       </c>
       <c r="D25" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>49</v>
@@ -3669,7 +3669,7 @@
         <v>48</v>
       </c>
       <c r="D26" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>49</v>
@@ -3686,7 +3686,7 @@
         <v>48</v>
       </c>
       <c r="D27" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>49</v>
@@ -3703,7 +3703,7 @@
         <v>48</v>
       </c>
       <c r="D28" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>49</v>
@@ -3720,7 +3720,7 @@
         <v>48</v>
       </c>
       <c r="D29" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>49</v>
@@ -3737,7 +3737,7 @@
         <v>48</v>
       </c>
       <c r="D30" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>49</v>
@@ -3754,7 +3754,7 @@
         <v>48</v>
       </c>
       <c r="D31" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>49</v>
@@ -3771,7 +3771,7 @@
         <v>48</v>
       </c>
       <c r="D32" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>49</v>
@@ -3788,7 +3788,7 @@
         <v>48</v>
       </c>
       <c r="D33" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>49</v>
@@ -3805,7 +3805,7 @@
         <v>48</v>
       </c>
       <c r="D34" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>49</v>
@@ -3822,7 +3822,7 @@
         <v>48</v>
       </c>
       <c r="D35" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>49</v>
@@ -3839,7 +3839,7 @@
         <v>48</v>
       </c>
       <c r="D36" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>49</v>
@@ -3856,7 +3856,7 @@
         <v>48</v>
       </c>
       <c r="D37" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>49</v>
@@ -3873,7 +3873,7 @@
         <v>48</v>
       </c>
       <c r="D38" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>49</v>
@@ -3890,7 +3890,7 @@
         <v>48</v>
       </c>
       <c r="D39" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>49</v>
@@ -3907,7 +3907,7 @@
         <v>48</v>
       </c>
       <c r="D40" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>49</v>
@@ -3924,7 +3924,7 @@
         <v>48</v>
       </c>
       <c r="D41" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>49</v>
@@ -3941,7 +3941,7 @@
         <v>48</v>
       </c>
       <c r="D42" s="2">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>49</v>
@@ -3958,7 +3958,7 @@
         <v>48</v>
       </c>
       <c r="D43" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>49</v>
@@ -3975,7 +3975,7 @@
         <v>48</v>
       </c>
       <c r="D44" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>49</v>
@@ -3992,7 +3992,7 @@
         <v>48</v>
       </c>
       <c r="D45" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>49</v>
@@ -4009,7 +4009,7 @@
         <v>48</v>
       </c>
       <c r="D46" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>49</v>
@@ -4026,7 +4026,7 @@
         <v>48</v>
       </c>
       <c r="D47" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>49</v>
@@ -4043,7 +4043,7 @@
         <v>48</v>
       </c>
       <c r="D48" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>49</v>
@@ -4060,7 +4060,7 @@
         <v>48</v>
       </c>
       <c r="D49" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>49</v>
@@ -4077,7 +4077,7 @@
         <v>48</v>
       </c>
       <c r="D50" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>49</v>
@@ -4094,7 +4094,7 @@
         <v>48</v>
       </c>
       <c r="D51" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>49</v>
@@ -4111,7 +4111,7 @@
         <v>48</v>
       </c>
       <c r="D52" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>49</v>
@@ -4128,7 +4128,7 @@
         <v>48</v>
       </c>
       <c r="D53" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>49</v>
@@ -4145,7 +4145,7 @@
         <v>48</v>
       </c>
       <c r="D54" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>49</v>
@@ -4162,7 +4162,7 @@
         <v>48</v>
       </c>
       <c r="D55" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>49</v>
@@ -4179,7 +4179,7 @@
         <v>48</v>
       </c>
       <c r="D56" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>49</v>
@@ -4196,7 +4196,7 @@
         <v>48</v>
       </c>
       <c r="D57" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>49</v>
@@ -4213,7 +4213,7 @@
         <v>48</v>
       </c>
       <c r="D58" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>49</v>
@@ -4230,7 +4230,7 @@
         <v>48</v>
       </c>
       <c r="D59" s="2">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>49</v>
@@ -4247,7 +4247,7 @@
         <v>48</v>
       </c>
       <c r="D60" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>49</v>
@@ -4264,7 +4264,7 @@
         <v>48</v>
       </c>
       <c r="D61" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>49</v>
@@ -4281,7 +4281,7 @@
         <v>48</v>
       </c>
       <c r="D62" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E62" s="2" t="s">
         <v>49</v>
@@ -4298,7 +4298,7 @@
         <v>48</v>
       </c>
       <c r="D63" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>49</v>
@@ -4315,7 +4315,7 @@
         <v>48</v>
       </c>
       <c r="D64" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>49</v>
@@ -4332,7 +4332,7 @@
         <v>48</v>
       </c>
       <c r="D65" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>49</v>
@@ -4349,7 +4349,7 @@
         <v>48</v>
       </c>
       <c r="D66" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>49</v>
@@ -4366,7 +4366,7 @@
         <v>48</v>
       </c>
       <c r="D67" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>49</v>
@@ -4383,7 +4383,7 @@
         <v>48</v>
       </c>
       <c r="D68" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>49</v>
@@ -4400,7 +4400,7 @@
         <v>48</v>
       </c>
       <c r="D69" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>49</v>
@@ -4417,7 +4417,7 @@
         <v>48</v>
       </c>
       <c r="D70" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>49</v>
@@ -4434,7 +4434,7 @@
         <v>48</v>
       </c>
       <c r="D71" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>49</v>
@@ -4451,7 +4451,7 @@
         <v>48</v>
       </c>
       <c r="D72" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>49</v>
@@ -4468,7 +4468,7 @@
         <v>48</v>
       </c>
       <c r="D73" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>49</v>
@@ -4485,7 +4485,7 @@
         <v>48</v>
       </c>
       <c r="D74" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>49</v>
@@ -4502,7 +4502,7 @@
         <v>48</v>
       </c>
       <c r="D75" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>49</v>
@@ -4519,7 +4519,7 @@
         <v>48</v>
       </c>
       <c r="D76" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>49</v>
@@ -4536,7 +4536,7 @@
         <v>48</v>
       </c>
       <c r="D77" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>49</v>
@@ -4553,7 +4553,7 @@
         <v>48</v>
       </c>
       <c r="D78" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>49</v>
@@ -4570,7 +4570,7 @@
         <v>48</v>
       </c>
       <c r="D79" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>49</v>
@@ -4587,7 +4587,7 @@
         <v>48</v>
       </c>
       <c r="D80" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>49</v>
@@ -4604,7 +4604,7 @@
         <v>48</v>
       </c>
       <c r="D81" s="2">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>49</v>
@@ -4621,7 +4621,7 @@
         <v>48</v>
       </c>
       <c r="D82" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>49</v>
@@ -4638,7 +4638,7 @@
         <v>48</v>
       </c>
       <c r="D83" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>49</v>
@@ -4655,7 +4655,7 @@
         <v>48</v>
       </c>
       <c r="D84" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>49</v>
@@ -4672,7 +4672,7 @@
         <v>48</v>
       </c>
       <c r="D85" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>49</v>
@@ -4689,7 +4689,7 @@
         <v>48</v>
       </c>
       <c r="D86" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>49</v>
@@ -4706,7 +4706,7 @@
         <v>48</v>
       </c>
       <c r="D87" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>49</v>
@@ -4723,7 +4723,7 @@
         <v>48</v>
       </c>
       <c r="D88" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>49</v>
@@ -4740,7 +4740,7 @@
         <v>48</v>
       </c>
       <c r="D89" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>49</v>
@@ -4757,7 +4757,7 @@
         <v>48</v>
       </c>
       <c r="D90" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>49</v>
@@ -4774,7 +4774,7 @@
         <v>48</v>
       </c>
       <c r="D91" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>49</v>
@@ -4791,7 +4791,7 @@
         <v>48</v>
       </c>
       <c r="D92" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>49</v>
@@ -4808,7 +4808,7 @@
         <v>48</v>
       </c>
       <c r="D93" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>49</v>
@@ -4825,7 +4825,7 @@
         <v>48</v>
       </c>
       <c r="D94" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>49</v>
@@ -4842,7 +4842,7 @@
         <v>48</v>
       </c>
       <c r="D95" s="2">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>49</v>
@@ -4859,7 +4859,7 @@
         <v>48</v>
       </c>
       <c r="D96" s="2">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>49</v>
@@ -4876,7 +4876,7 @@
         <v>48</v>
       </c>
       <c r="D97" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>49</v>
@@ -4893,7 +4893,7 @@
         <v>48</v>
       </c>
       <c r="D98" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>49</v>
@@ -4910,7 +4910,7 @@
         <v>48</v>
       </c>
       <c r="D99" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>49</v>
@@ -4927,7 +4927,7 @@
         <v>48</v>
       </c>
       <c r="D100" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>49</v>
@@ -4944,7 +4944,7 @@
         <v>48</v>
       </c>
       <c r="D101" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>49</v>
@@ -4961,7 +4961,7 @@
         <v>48</v>
       </c>
       <c r="D102" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>49</v>
@@ -4978,7 +4978,7 @@
         <v>48</v>
       </c>
       <c r="D103" s="2">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>49</v>
@@ -4995,7 +4995,7 @@
         <v>48</v>
       </c>
       <c r="D104" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>49</v>
@@ -5012,7 +5012,7 @@
         <v>48</v>
       </c>
       <c r="D105" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>49</v>
@@ -5029,7 +5029,7 @@
         <v>48</v>
       </c>
       <c r="D106" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>49</v>
@@ -5046,7 +5046,7 @@
         <v>48</v>
       </c>
       <c r="D107" s="2">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>49</v>
@@ -5063,7 +5063,7 @@
         <v>48</v>
       </c>
       <c r="D108" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>49</v>
@@ -5097,7 +5097,7 @@
         <v>48</v>
       </c>
       <c r="D110" s="2">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E110" s="2" t="s">
         <v>49</v>
@@ -5114,7 +5114,7 @@
         <v>48</v>
       </c>
       <c r="D111" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E111" s="2" t="s">
         <v>49</v>
@@ -5131,7 +5131,7 @@
         <v>48</v>
       </c>
       <c r="D112" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>49</v>
@@ -5148,7 +5148,7 @@
         <v>48</v>
       </c>
       <c r="D113" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>49</v>
@@ -5165,7 +5165,7 @@
         <v>48</v>
       </c>
       <c r="D114" s="2">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>49</v>
@@ -5182,7 +5182,7 @@
         <v>48</v>
       </c>
       <c r="D115" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>49</v>
@@ -5199,7 +5199,7 @@
         <v>48</v>
       </c>
       <c r="D116" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E116" s="2" t="s">
         <v>49</v>
@@ -5233,7 +5233,7 @@
         <v>48</v>
       </c>
       <c r="D118" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E118" s="2" t="s">
         <v>49</v>
@@ -5250,7 +5250,7 @@
         <v>48</v>
       </c>
       <c r="D119" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>49</v>
@@ -5267,7 +5267,7 @@
         <v>48</v>
       </c>
       <c r="D120" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>49</v>
@@ -5284,7 +5284,7 @@
         <v>48</v>
       </c>
       <c r="D121" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>49</v>
@@ -5301,7 +5301,7 @@
         <v>48</v>
       </c>
       <c r="D122" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>49</v>
@@ -5318,7 +5318,7 @@
         <v>48</v>
       </c>
       <c r="D123" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>49</v>
@@ -5335,7 +5335,7 @@
         <v>48</v>
       </c>
       <c r="D124" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>49</v>
@@ -5352,7 +5352,7 @@
         <v>48</v>
       </c>
       <c r="D125" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>49</v>
@@ -5369,7 +5369,7 @@
         <v>48</v>
       </c>
       <c r="D126" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>49</v>
@@ -5386,7 +5386,7 @@
         <v>48</v>
       </c>
       <c r="D127" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E127" s="2" t="s">
         <v>49</v>
@@ -5403,7 +5403,7 @@
         <v>48</v>
       </c>
       <c r="D128" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>49</v>
@@ -5420,7 +5420,7 @@
         <v>48</v>
       </c>
       <c r="D129" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>49</v>
@@ -5437,7 +5437,7 @@
         <v>48</v>
       </c>
       <c r="D130" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E130" s="2" t="s">
         <v>49</v>
@@ -5454,7 +5454,7 @@
         <v>48</v>
       </c>
       <c r="D131" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E131" s="2" t="s">
         <v>49</v>
@@ -5471,7 +5471,7 @@
         <v>48</v>
       </c>
       <c r="D132" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E132" s="2" t="s">
         <v>49</v>
@@ -5488,7 +5488,7 @@
         <v>48</v>
       </c>
       <c r="D133" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>49</v>
@@ -5505,7 +5505,7 @@
         <v>48</v>
       </c>
       <c r="D134" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E134" s="2" t="s">
         <v>49</v>
@@ -5522,7 +5522,7 @@
         <v>48</v>
       </c>
       <c r="D135" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E135" s="2" t="s">
         <v>49</v>
@@ -5556,7 +5556,7 @@
         <v>48</v>
       </c>
       <c r="D137" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>49</v>
@@ -5573,7 +5573,7 @@
         <v>48</v>
       </c>
       <c r="D138" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>49</v>
@@ -5590,7 +5590,7 @@
         <v>48</v>
       </c>
       <c r="D139" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E139" s="2" t="s">
         <v>49</v>
@@ -5607,7 +5607,7 @@
         <v>48</v>
       </c>
       <c r="D140" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E140" s="2" t="s">
         <v>49</v>
@@ -5624,7 +5624,7 @@
         <v>48</v>
       </c>
       <c r="D141" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>49</v>
@@ -5641,7 +5641,7 @@
         <v>48</v>
       </c>
       <c r="D142" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>49</v>
@@ -5658,7 +5658,7 @@
         <v>48</v>
       </c>
       <c r="D143" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E143" s="2" t="s">
         <v>49</v>
@@ -5675,7 +5675,7 @@
         <v>48</v>
       </c>
       <c r="D144" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E144" s="2" t="s">
         <v>49</v>
@@ -5692,7 +5692,7 @@
         <v>48</v>
       </c>
       <c r="D145" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>49</v>
@@ -5709,7 +5709,7 @@
         <v>48</v>
       </c>
       <c r="D146" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E146" s="2" t="s">
         <v>49</v>
@@ -5726,7 +5726,7 @@
         <v>48</v>
       </c>
       <c r="D147" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>49</v>
@@ -5743,7 +5743,7 @@
         <v>48</v>
       </c>
       <c r="D148" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E148" s="2" t="s">
         <v>49</v>
@@ -5760,7 +5760,7 @@
         <v>48</v>
       </c>
       <c r="D149" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E149" s="2" t="s">
         <v>49</v>
@@ -5777,7 +5777,7 @@
         <v>48</v>
       </c>
       <c r="D150" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E150" s="2" t="s">
         <v>49</v>
@@ -5811,7 +5811,7 @@
         <v>48</v>
       </c>
       <c r="D152" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>49</v>
@@ -5828,7 +5828,7 @@
         <v>48</v>
       </c>
       <c r="D153" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>49</v>
@@ -5845,7 +5845,7 @@
         <v>48</v>
       </c>
       <c r="D154" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>49</v>
@@ -5862,7 +5862,7 @@
         <v>48</v>
       </c>
       <c r="D155" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>49</v>
@@ -5879,7 +5879,7 @@
         <v>48</v>
       </c>
       <c r="D156" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>49</v>
@@ -5896,7 +5896,7 @@
         <v>48</v>
       </c>
       <c r="D157" s="2">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>49</v>
@@ -5913,7 +5913,7 @@
         <v>48</v>
       </c>
       <c r="D158" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>49</v>
@@ -5930,7 +5930,7 @@
         <v>48</v>
       </c>
       <c r="D159" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>49</v>
@@ -5947,7 +5947,7 @@
         <v>48</v>
       </c>
       <c r="D160" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>49</v>
@@ -5964,7 +5964,7 @@
         <v>48</v>
       </c>
       <c r="D161" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>49</v>
@@ -5998,7 +5998,7 @@
         <v>48</v>
       </c>
       <c r="D163" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>49</v>
@@ -6015,7 +6015,7 @@
         <v>48</v>
       </c>
       <c r="D164" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>49</v>
@@ -6032,7 +6032,7 @@
         <v>48</v>
       </c>
       <c r="D165" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>49</v>
@@ -6049,7 +6049,7 @@
         <v>48</v>
       </c>
       <c r="D166" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E166" s="2" t="s">
         <v>49</v>
@@ -6083,7 +6083,7 @@
         <v>48</v>
       </c>
       <c r="D168" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E168" s="2" t="s">
         <v>49</v>
@@ -6100,7 +6100,7 @@
         <v>48</v>
       </c>
       <c r="D169" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E169" s="2" t="s">
         <v>49</v>
@@ -6117,7 +6117,7 @@
         <v>48</v>
       </c>
       <c r="D170" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E170" s="2" t="s">
         <v>49</v>
@@ -6134,7 +6134,7 @@
         <v>48</v>
       </c>
       <c r="D171" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>49</v>
@@ -6151,7 +6151,7 @@
         <v>48</v>
       </c>
       <c r="D172" s="2">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E172" s="2" t="s">
         <v>49</v>
@@ -6168,7 +6168,7 @@
         <v>48</v>
       </c>
       <c r="D173" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E173" s="2" t="s">
         <v>49</v>
@@ -6185,7 +6185,7 @@
         <v>48</v>
       </c>
       <c r="D174" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E174" s="2" t="s">
         <v>49</v>
@@ -6202,7 +6202,7 @@
         <v>48</v>
       </c>
       <c r="D175" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E175" s="2" t="s">
         <v>49</v>
@@ -6219,7 +6219,7 @@
         <v>48</v>
       </c>
       <c r="D176" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E176" s="2" t="s">
         <v>49</v>
@@ -6236,7 +6236,7 @@
         <v>48</v>
       </c>
       <c r="D177" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E177" s="2" t="s">
         <v>49</v>
@@ -6253,7 +6253,7 @@
         <v>48</v>
       </c>
       <c r="D178" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E178" s="2" t="s">
         <v>49</v>
@@ -6270,7 +6270,7 @@
         <v>48</v>
       </c>
       <c r="D179" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E179" s="2" t="s">
         <v>49</v>
@@ -6287,7 +6287,7 @@
         <v>48</v>
       </c>
       <c r="D180" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E180" s="2" t="s">
         <v>49</v>
@@ -6304,7 +6304,7 @@
         <v>48</v>
       </c>
       <c r="D181" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>49</v>
@@ -6321,7 +6321,7 @@
         <v>48</v>
       </c>
       <c r="D182" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E182" s="2" t="s">
         <v>49</v>
@@ -6338,7 +6338,7 @@
         <v>48</v>
       </c>
       <c r="D183" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>49</v>
@@ -6355,7 +6355,7 @@
         <v>48</v>
       </c>
       <c r="D184" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>49</v>
@@ -6372,7 +6372,7 @@
         <v>48</v>
       </c>
       <c r="D185" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>49</v>
@@ -6389,7 +6389,7 @@
         <v>48</v>
       </c>
       <c r="D186" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E186" s="2" t="s">
         <v>49</v>
@@ -6406,7 +6406,7 @@
         <v>48</v>
       </c>
       <c r="D187" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>49</v>
@@ -6423,7 +6423,7 @@
         <v>48</v>
       </c>
       <c r="D188" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>49</v>
@@ -6440,7 +6440,7 @@
         <v>48</v>
       </c>
       <c r="D189" s="2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>49</v>
@@ -6457,7 +6457,7 @@
         <v>48</v>
       </c>
       <c r="D190" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E190" s="2" t="s">
         <v>49</v>
@@ -6474,7 +6474,7 @@
         <v>48</v>
       </c>
       <c r="D191" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>49</v>
@@ -6491,7 +6491,7 @@
         <v>48</v>
       </c>
       <c r="D192" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>49</v>
@@ -6508,7 +6508,7 @@
         <v>48</v>
       </c>
       <c r="D193" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E193" s="2" t="s">
         <v>49</v>
@@ -6542,7 +6542,7 @@
         <v>48</v>
       </c>
       <c r="D195" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E195" s="2" t="s">
         <v>49</v>
@@ -6559,7 +6559,7 @@
         <v>48</v>
       </c>
       <c r="D196" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E196" s="2" t="s">
         <v>49</v>
@@ -6576,7 +6576,7 @@
         <v>48</v>
       </c>
       <c r="D197" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E197" s="2" t="s">
         <v>49</v>
@@ -6593,7 +6593,7 @@
         <v>48</v>
       </c>
       <c r="D198" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E198" s="2" t="s">
         <v>49</v>
@@ -6610,7 +6610,7 @@
         <v>48</v>
       </c>
       <c r="D199" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E199" s="2" t="s">
         <v>49</v>
@@ -6627,7 +6627,7 @@
         <v>48</v>
       </c>
       <c r="D200" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E200" s="2" t="s">
         <v>49</v>
@@ -6644,7 +6644,7 @@
         <v>48</v>
       </c>
       <c r="D201" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E201" s="2" t="s">
         <v>49</v>
@@ -6661,7 +6661,7 @@
         <v>48</v>
       </c>
       <c r="D202" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E202" s="2" t="s">
         <v>49</v>
@@ -6678,7 +6678,7 @@
         <v>48</v>
       </c>
       <c r="D203" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E203" s="2" t="s">
         <v>49</v>
@@ -6712,7 +6712,7 @@
         <v>48</v>
       </c>
       <c r="D205" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E205" s="2" t="s">
         <v>49</v>
@@ -6729,7 +6729,7 @@
         <v>48</v>
       </c>
       <c r="D206" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E206" s="2" t="s">
         <v>49</v>
@@ -6746,7 +6746,7 @@
         <v>48</v>
       </c>
       <c r="D207" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E207" s="2" t="s">
         <v>49</v>
@@ -6763,7 +6763,7 @@
         <v>48</v>
       </c>
       <c r="D208" s="2">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E208" s="2" t="s">
         <v>49</v>
@@ -6780,7 +6780,7 @@
         <v>48</v>
       </c>
       <c r="D209" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E209" s="2" t="s">
         <v>49</v>
@@ -6797,7 +6797,7 @@
         <v>48</v>
       </c>
       <c r="D210" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E210" s="2" t="s">
         <v>49</v>
@@ -6814,7 +6814,7 @@
         <v>48</v>
       </c>
       <c r="D211" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E211" s="2" t="s">
         <v>49</v>
@@ -6848,7 +6848,7 @@
         <v>48</v>
       </c>
       <c r="D213" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E213" s="2" t="s">
         <v>49</v>
@@ -6865,7 +6865,7 @@
         <v>48</v>
       </c>
       <c r="D214" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E214" s="2" t="s">
         <v>49</v>
@@ -6882,7 +6882,7 @@
         <v>48</v>
       </c>
       <c r="D215" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E215" s="2" t="s">
         <v>49</v>
@@ -6899,7 +6899,7 @@
         <v>48</v>
       </c>
       <c r="D216" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E216" s="2" t="s">
         <v>49</v>
@@ -6916,7 +6916,7 @@
         <v>48</v>
       </c>
       <c r="D217" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>49</v>
@@ -6933,7 +6933,7 @@
         <v>48</v>
       </c>
       <c r="D218" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E218" s="2" t="s">
         <v>49</v>
@@ -6950,7 +6950,7 @@
         <v>48</v>
       </c>
       <c r="D219" s="2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E219" s="2" t="s">
         <v>49</v>
@@ -6967,7 +6967,7 @@
         <v>48</v>
       </c>
       <c r="D220" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E220" s="2" t="s">
         <v>49</v>
@@ -6984,7 +6984,7 @@
         <v>48</v>
       </c>
       <c r="D221" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>49</v>
@@ -7001,7 +7001,7 @@
         <v>48</v>
       </c>
       <c r="D222" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>49</v>
@@ -7018,7 +7018,7 @@
         <v>48</v>
       </c>
       <c r="D223" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E223" s="2" t="s">
         <v>49</v>
@@ -7052,7 +7052,7 @@
         <v>48</v>
       </c>
       <c r="D225" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E225" s="2" t="s">
         <v>49</v>
@@ -7069,7 +7069,7 @@
         <v>48</v>
       </c>
       <c r="D226" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E226" s="2" t="s">
         <v>49</v>
@@ -7086,7 +7086,7 @@
         <v>48</v>
       </c>
       <c r="D227" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E227" s="2" t="s">
         <v>49</v>
@@ -7103,7 +7103,7 @@
         <v>48</v>
       </c>
       <c r="D228" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E228" s="2" t="s">
         <v>49</v>
@@ -7120,7 +7120,7 @@
         <v>48</v>
       </c>
       <c r="D229" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E229" s="2" t="s">
         <v>49</v>
@@ -7137,7 +7137,7 @@
         <v>48</v>
       </c>
       <c r="D230" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E230" s="2" t="s">
         <v>49</v>
@@ -7154,7 +7154,7 @@
         <v>48</v>
       </c>
       <c r="D231" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E231" s="2" t="s">
         <v>49</v>
@@ -7171,7 +7171,7 @@
         <v>48</v>
       </c>
       <c r="D232" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E232" s="2" t="s">
         <v>49</v>
@@ -7188,7 +7188,7 @@
         <v>48</v>
       </c>
       <c r="D233" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>49</v>
@@ -7205,7 +7205,7 @@
         <v>48</v>
       </c>
       <c r="D234" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E234" s="2" t="s">
         <v>49</v>
@@ -7222,7 +7222,7 @@
         <v>48</v>
       </c>
       <c r="D235" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>49</v>
@@ -7239,7 +7239,7 @@
         <v>48</v>
       </c>
       <c r="D236" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E236" s="2" t="s">
         <v>49</v>
@@ -7256,7 +7256,7 @@
         <v>48</v>
       </c>
       <c r="D237" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>49</v>
@@ -7273,7 +7273,7 @@
         <v>48</v>
       </c>
       <c r="D238" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E238" s="2" t="s">
         <v>49</v>
@@ -7290,7 +7290,7 @@
         <v>48</v>
       </c>
       <c r="D239" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>49</v>
@@ -7307,7 +7307,7 @@
         <v>48</v>
       </c>
       <c r="D240" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E240" s="2" t="s">
         <v>49</v>
@@ -7324,7 +7324,7 @@
         <v>48</v>
       </c>
       <c r="D241" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>49</v>
@@ -7341,7 +7341,7 @@
         <v>48</v>
       </c>
       <c r="D242" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E242" s="2" t="s">
         <v>49</v>
@@ -7358,7 +7358,7 @@
         <v>48</v>
       </c>
       <c r="D243" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E243" s="2" t="s">
         <v>49</v>
@@ -7375,7 +7375,7 @@
         <v>48</v>
       </c>
       <c r="D244" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E244" s="2" t="s">
         <v>49</v>
@@ -7392,7 +7392,7 @@
         <v>48</v>
       </c>
       <c r="D245" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E245" s="2" t="s">
         <v>49</v>
@@ -7409,7 +7409,7 @@
         <v>48</v>
       </c>
       <c r="D246" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E246" s="2" t="s">
         <v>49</v>
@@ -7426,7 +7426,7 @@
         <v>48</v>
       </c>
       <c r="D247" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E247" s="2" t="s">
         <v>49</v>
@@ -7443,7 +7443,7 @@
         <v>48</v>
       </c>
       <c r="D248" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E248" s="2" t="s">
         <v>49</v>
@@ -7460,7 +7460,7 @@
         <v>48</v>
       </c>
       <c r="D249" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E249" s="2" t="s">
         <v>49</v>
@@ -7477,7 +7477,7 @@
         <v>48</v>
       </c>
       <c r="D250" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E250" s="2" t="s">
         <v>49</v>
@@ -7494,7 +7494,7 @@
         <v>48</v>
       </c>
       <c r="D251" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>49</v>
@@ -7528,7 +7528,7 @@
         <v>48</v>
       </c>
       <c r="D253" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>49</v>
@@ -7545,7 +7545,7 @@
         <v>48</v>
       </c>
       <c r="D254" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E254" s="2" t="s">
         <v>49</v>
@@ -7562,7 +7562,7 @@
         <v>48</v>
       </c>
       <c r="D255" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E255" s="2" t="s">
         <v>49</v>
@@ -7579,7 +7579,7 @@
         <v>48</v>
       </c>
       <c r="D256" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E256" s="2" t="s">
         <v>49</v>
@@ -7596,7 +7596,7 @@
         <v>48</v>
       </c>
       <c r="D257" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E257" s="2" t="s">
         <v>49</v>
@@ -7613,7 +7613,7 @@
         <v>48</v>
       </c>
       <c r="D258" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E258" s="2" t="s">
         <v>49</v>
@@ -7630,7 +7630,7 @@
         <v>48</v>
       </c>
       <c r="D259" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E259" s="2" t="s">
         <v>49</v>
@@ -7647,7 +7647,7 @@
         <v>48</v>
       </c>
       <c r="D260" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E260" s="2" t="s">
         <v>49</v>
@@ -7664,7 +7664,7 @@
         <v>48</v>
       </c>
       <c r="D261" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E261" s="2" t="s">
         <v>49</v>
@@ -7681,7 +7681,7 @@
         <v>48</v>
       </c>
       <c r="D262" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E262" s="2" t="s">
         <v>49</v>
@@ -7698,7 +7698,7 @@
         <v>48</v>
       </c>
       <c r="D263" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E263" s="2" t="s">
         <v>49</v>
@@ -7715,7 +7715,7 @@
         <v>48</v>
       </c>
       <c r="D264" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E264" s="2" t="s">
         <v>49</v>
@@ -7732,7 +7732,7 @@
         <v>48</v>
       </c>
       <c r="D265" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>49</v>
@@ -7749,7 +7749,7 @@
         <v>48</v>
       </c>
       <c r="D266" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E266" s="2" t="s">
         <v>49</v>
@@ -7766,7 +7766,7 @@
         <v>48</v>
       </c>
       <c r="D267" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E267" s="2" t="s">
         <v>49</v>
@@ -7783,7 +7783,7 @@
         <v>48</v>
       </c>
       <c r="D268" s="2">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E268" s="2" t="s">
         <v>49</v>
@@ -7800,7 +7800,7 @@
         <v>48</v>
       </c>
       <c r="D269" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>49</v>
@@ -7817,7 +7817,7 @@
         <v>48</v>
       </c>
       <c r="D270" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E270" s="2" t="s">
         <v>49</v>
@@ -7834,7 +7834,7 @@
         <v>48</v>
       </c>
       <c r="D271" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>49</v>
@@ -7851,7 +7851,7 @@
         <v>48</v>
       </c>
       <c r="D272" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E272" s="2" t="s">
         <v>49</v>
@@ -7868,7 +7868,7 @@
         <v>48</v>
       </c>
       <c r="D273" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E273" s="2" t="s">
         <v>49</v>
@@ -7885,7 +7885,7 @@
         <v>48</v>
       </c>
       <c r="D274" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E274" s="2" t="s">
         <v>49</v>
@@ -7902,7 +7902,7 @@
         <v>48</v>
       </c>
       <c r="D275" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E275" s="2" t="s">
         <v>49</v>
@@ -7919,7 +7919,7 @@
         <v>48</v>
       </c>
       <c r="D276" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E276" s="2" t="s">
         <v>49</v>
@@ -7936,7 +7936,7 @@
         <v>48</v>
       </c>
       <c r="D277" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E277" s="2" t="s">
         <v>49</v>
@@ -7953,7 +7953,7 @@
         <v>48</v>
       </c>
       <c r="D278" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E278" s="2" t="s">
         <v>49</v>
@@ -7970,7 +7970,7 @@
         <v>48</v>
       </c>
       <c r="D279" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E279" s="2" t="s">
         <v>49</v>
@@ -7987,7 +7987,7 @@
         <v>48</v>
       </c>
       <c r="D280" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E280" s="2" t="s">
         <v>49</v>
@@ -8004,7 +8004,7 @@
         <v>48</v>
       </c>
       <c r="D281" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E281" s="2" t="s">
         <v>49</v>
@@ -8021,7 +8021,7 @@
         <v>48</v>
       </c>
       <c r="D282" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E282" s="2" t="s">
         <v>49</v>
@@ -8038,7 +8038,7 @@
         <v>48</v>
       </c>
       <c r="D283" s="2">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="E283" s="2" t="s">
         <v>49</v>
@@ -8055,7 +8055,7 @@
         <v>48</v>
       </c>
       <c r="D284" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E284" s="2" t="s">
         <v>49</v>
@@ -8072,7 +8072,7 @@
         <v>48</v>
       </c>
       <c r="D285" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E285" s="2" t="s">
         <v>49</v>
@@ -8089,7 +8089,7 @@
         <v>48</v>
       </c>
       <c r="D286" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E286" s="2" t="s">
         <v>49</v>
@@ -8106,7 +8106,7 @@
         <v>48</v>
       </c>
       <c r="D287" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E287" s="2" t="s">
         <v>49</v>
@@ -8123,7 +8123,7 @@
         <v>48</v>
       </c>
       <c r="D288" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E288" s="2" t="s">
         <v>49</v>
@@ -8140,7 +8140,7 @@
         <v>48</v>
       </c>
       <c r="D289" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E289" s="2" t="s">
         <v>49</v>
@@ -8157,7 +8157,7 @@
         <v>48</v>
       </c>
       <c r="D290" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E290" s="2" t="s">
         <v>49</v>
@@ -8174,7 +8174,7 @@
         <v>48</v>
       </c>
       <c r="D291" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E291" s="2" t="s">
         <v>49</v>
@@ -8191,7 +8191,7 @@
         <v>48</v>
       </c>
       <c r="D292" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E292" s="2" t="s">
         <v>49</v>
@@ -8208,7 +8208,7 @@
         <v>48</v>
       </c>
       <c r="D293" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E293" s="2" t="s">
         <v>49</v>
@@ -8242,7 +8242,7 @@
         <v>48</v>
       </c>
       <c r="D295" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E295" s="2" t="s">
         <v>49</v>
@@ -8259,7 +8259,7 @@
         <v>48</v>
       </c>
       <c r="D296" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E296" s="2" t="s">
         <v>49</v>
@@ -8276,7 +8276,7 @@
         <v>48</v>
       </c>
       <c r="D297" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E297" s="2" t="s">
         <v>49</v>
@@ -8293,7 +8293,7 @@
         <v>48</v>
       </c>
       <c r="D298" s="2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E298" s="2" t="s">
         <v>49</v>
@@ -8310,7 +8310,7 @@
         <v>48</v>
       </c>
       <c r="D299" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E299" s="2" t="s">
         <v>49</v>
@@ -8327,7 +8327,7 @@
         <v>48</v>
       </c>
       <c r="D300" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E300" s="2" t="s">
         <v>49</v>
@@ -8344,7 +8344,7 @@
         <v>48</v>
       </c>
       <c r="D301" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E301" s="2" t="s">
         <v>49</v>
@@ -8361,7 +8361,7 @@
         <v>48</v>
       </c>
       <c r="D302" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E302" s="2" t="s">
         <v>49</v>
@@ -8378,7 +8378,7 @@
         <v>48</v>
       </c>
       <c r="D303" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E303" s="2" t="s">
         <v>49</v>
@@ -8395,7 +8395,7 @@
         <v>48</v>
       </c>
       <c r="D304" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E304" s="2" t="s">
         <v>49</v>
@@ -8412,7 +8412,7 @@
         <v>48</v>
       </c>
       <c r="D305" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E305" s="2" t="s">
         <v>49</v>
@@ -8429,7 +8429,7 @@
         <v>48</v>
       </c>
       <c r="D306" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E306" s="2" t="s">
         <v>49</v>
@@ -8446,7 +8446,7 @@
         <v>48</v>
       </c>
       <c r="D307" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E307" s="2" t="s">
         <v>49</v>
@@ -8463,7 +8463,7 @@
         <v>48</v>
       </c>
       <c r="D308" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E308" s="2" t="s">
         <v>49</v>
@@ -8514,7 +8514,7 @@
         <v>48</v>
       </c>
       <c r="D311" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E311" s="2" t="s">
         <v>49</v>
@@ -8531,7 +8531,7 @@
         <v>48</v>
       </c>
       <c r="D312" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E312" s="2" t="s">
         <v>49</v>
@@ -8548,7 +8548,7 @@
         <v>48</v>
       </c>
       <c r="D313" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E313" s="2" t="s">
         <v>49</v>
@@ -8565,7 +8565,7 @@
         <v>48</v>
       </c>
       <c r="D314" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E314" s="2" t="s">
         <v>49</v>
@@ -8582,7 +8582,7 @@
         <v>48</v>
       </c>
       <c r="D315" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E315" s="2" t="s">
         <v>49</v>
@@ -8599,7 +8599,7 @@
         <v>48</v>
       </c>
       <c r="D316" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E316" s="2" t="s">
         <v>49</v>
@@ -8616,7 +8616,7 @@
         <v>48</v>
       </c>
       <c r="D317" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E317" s="2" t="s">
         <v>49</v>
@@ -8633,7 +8633,7 @@
         <v>48</v>
       </c>
       <c r="D318" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E318" s="2" t="s">
         <v>49</v>
@@ -8650,7 +8650,7 @@
         <v>48</v>
       </c>
       <c r="D319" s="2">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E319" s="2" t="s">
         <v>49</v>
@@ -8667,7 +8667,7 @@
         <v>48</v>
       </c>
       <c r="D320" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E320" s="2" t="s">
         <v>49</v>
@@ -8701,7 +8701,7 @@
         <v>48</v>
       </c>
       <c r="D322" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E322" s="2" t="s">
         <v>49</v>
@@ -8718,7 +8718,7 @@
         <v>48</v>
       </c>
       <c r="D323" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E323" s="2" t="s">
         <v>49</v>
@@ -8752,7 +8752,7 @@
         <v>48</v>
       </c>
       <c r="D325" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E325" s="2" t="s">
         <v>49</v>
@@ -8769,7 +8769,7 @@
         <v>48</v>
       </c>
       <c r="D326" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E326" s="2" t="s">
         <v>49</v>
@@ -8786,7 +8786,7 @@
         <v>48</v>
       </c>
       <c r="D327" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E327" s="2" t="s">
         <v>49</v>
@@ -8803,7 +8803,7 @@
         <v>48</v>
       </c>
       <c r="D328" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E328" s="2" t="s">
         <v>49</v>
@@ -8820,7 +8820,7 @@
         <v>48</v>
       </c>
       <c r="D329" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E329" s="2" t="s">
         <v>49</v>
@@ -8837,7 +8837,7 @@
         <v>48</v>
       </c>
       <c r="D330" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E330" s="2" t="s">
         <v>49</v>
@@ -8854,7 +8854,7 @@
         <v>48</v>
       </c>
       <c r="D331" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E331" s="2" t="s">
         <v>49</v>
@@ -8871,7 +8871,7 @@
         <v>48</v>
       </c>
       <c r="D332" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E332" s="2" t="s">
         <v>49</v>
@@ -8888,7 +8888,7 @@
         <v>48</v>
       </c>
       <c r="D333" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E333" s="2" t="s">
         <v>49</v>
@@ -8905,7 +8905,7 @@
         <v>48</v>
       </c>
       <c r="D334" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E334" s="2" t="s">
         <v>49</v>
@@ -8956,7 +8956,7 @@
         <v>48</v>
       </c>
       <c r="D337" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E337" s="2" t="s">
         <v>49</v>
@@ -8973,7 +8973,7 @@
         <v>48</v>
       </c>
       <c r="D338" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E338" s="2" t="s">
         <v>49</v>
@@ -8990,7 +8990,7 @@
         <v>48</v>
       </c>
       <c r="D339" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E339" s="2" t="s">
         <v>49</v>
@@ -9007,7 +9007,7 @@
         <v>48</v>
       </c>
       <c r="D340" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E340" s="2" t="s">
         <v>49</v>
@@ -9024,7 +9024,7 @@
         <v>48</v>
       </c>
       <c r="D341" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E341" s="2" t="s">
         <v>49</v>
@@ -9041,7 +9041,7 @@
         <v>48</v>
       </c>
       <c r="D342" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E342" s="2" t="s">
         <v>49</v>
@@ -9058,7 +9058,7 @@
         <v>48</v>
       </c>
       <c r="D343" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E343" s="2" t="s">
         <v>49</v>
@@ -9075,7 +9075,7 @@
         <v>48</v>
       </c>
       <c r="D344" s="2">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E344" s="2" t="s">
         <v>49</v>
@@ -9092,7 +9092,7 @@
         <v>48</v>
       </c>
       <c r="D345" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E345" s="2" t="s">
         <v>49</v>
@@ -9109,7 +9109,7 @@
         <v>48</v>
       </c>
       <c r="D346" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E346" s="2" t="s">
         <v>49</v>
@@ -9126,7 +9126,7 @@
         <v>48</v>
       </c>
       <c r="D347" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E347" s="2" t="s">
         <v>49</v>
@@ -9143,7 +9143,7 @@
         <v>48</v>
       </c>
       <c r="D348" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E348" s="2" t="s">
         <v>49</v>
@@ -9160,7 +9160,7 @@
         <v>48</v>
       </c>
       <c r="D349" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E349" s="2" t="s">
         <v>49</v>
@@ -9177,7 +9177,7 @@
         <v>48</v>
       </c>
       <c r="D350" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E350" s="2" t="s">
         <v>49</v>
@@ -9194,7 +9194,7 @@
         <v>48</v>
       </c>
       <c r="D351" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E351" s="2" t="s">
         <v>49</v>
@@ -9211,7 +9211,7 @@
         <v>48</v>
       </c>
       <c r="D352" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E352" s="2" t="s">
         <v>49</v>
@@ -9228,7 +9228,7 @@
         <v>48</v>
       </c>
       <c r="D353" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E353" s="2" t="s">
         <v>49</v>
@@ -9245,7 +9245,7 @@
         <v>48</v>
       </c>
       <c r="D354" s="2">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E354" s="2" t="s">
         <v>49</v>
@@ -9262,7 +9262,7 @@
         <v>48</v>
       </c>
       <c r="D355" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E355" s="2" t="s">
         <v>49</v>
@@ -9279,7 +9279,7 @@
         <v>48</v>
       </c>
       <c r="D356" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E356" s="2" t="s">
         <v>49</v>
@@ -9296,7 +9296,7 @@
         <v>48</v>
       </c>
       <c r="D357" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E357" s="2" t="s">
         <v>49</v>
@@ -9313,7 +9313,7 @@
         <v>48</v>
       </c>
       <c r="D358" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E358" s="2" t="s">
         <v>49</v>
@@ -9330,7 +9330,7 @@
         <v>48</v>
       </c>
       <c r="D359" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E359" s="2" t="s">
         <v>49</v>
@@ -9347,7 +9347,7 @@
         <v>48</v>
       </c>
       <c r="D360" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E360" s="2" t="s">
         <v>49</v>
@@ -9364,7 +9364,7 @@
         <v>48</v>
       </c>
       <c r="D361" s="2">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E361" s="2" t="s">
         <v>49</v>
@@ -9381,7 +9381,7 @@
         <v>48</v>
       </c>
       <c r="D362" s="2">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="E362" s="2" t="s">
         <v>49</v>
@@ -9398,7 +9398,7 @@
         <v>48</v>
       </c>
       <c r="D363" s="2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E363" s="2" t="s">
         <v>49</v>
@@ -9415,7 +9415,7 @@
         <v>48</v>
       </c>
       <c r="D364" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E364" s="2" t="s">
         <v>49</v>
@@ -9432,7 +9432,7 @@
         <v>48</v>
       </c>
       <c r="D365" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E365" s="2" t="s">
         <v>49</v>
@@ -9449,7 +9449,7 @@
         <v>48</v>
       </c>
       <c r="D366" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E366" s="2" t="s">
         <v>49</v>
@@ -9466,7 +9466,7 @@
         <v>48</v>
       </c>
       <c r="D367" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E367" s="2" t="s">
         <v>49</v>
@@ -9483,7 +9483,7 @@
         <v>48</v>
       </c>
       <c r="D368" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E368" s="2" t="s">
         <v>49</v>
@@ -9500,7 +9500,7 @@
         <v>48</v>
       </c>
       <c r="D369" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E369" s="2" t="s">
         <v>49</v>
@@ -9517,7 +9517,7 @@
         <v>48</v>
       </c>
       <c r="D370" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E370" s="2" t="s">
         <v>49</v>
@@ -9534,7 +9534,7 @@
         <v>48</v>
       </c>
       <c r="D371" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E371" s="2" t="s">
         <v>49</v>
@@ -9568,7 +9568,7 @@
         <v>48</v>
       </c>
       <c r="D373" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E373" s="2" t="s">
         <v>49</v>
@@ -9585,7 +9585,7 @@
         <v>48</v>
       </c>
       <c r="D374" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E374" s="2" t="s">
         <v>49</v>
@@ -9602,7 +9602,7 @@
         <v>48</v>
       </c>
       <c r="D375" s="2">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E375" s="2" t="s">
         <v>49</v>
@@ -9619,7 +9619,7 @@
         <v>48</v>
       </c>
       <c r="D376" s="2">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="E376" s="2" t="s">
         <v>49</v>
@@ -9636,7 +9636,7 @@
         <v>48</v>
       </c>
       <c r="D377" s="2">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="E377" s="2" t="s">
         <v>49</v>
@@ -9653,7 +9653,7 @@
         <v>48</v>
       </c>
       <c r="D378" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E378" s="2" t="s">
         <v>49</v>
@@ -9670,7 +9670,7 @@
         <v>48</v>
       </c>
       <c r="D379" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E379" s="2" t="s">
         <v>49</v>
@@ -9687,7 +9687,7 @@
         <v>48</v>
       </c>
       <c r="D380" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E380" s="2" t="s">
         <v>49</v>
@@ -9704,7 +9704,7 @@
         <v>48</v>
       </c>
       <c r="D381" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E381" s="2" t="s">
         <v>49</v>
@@ -9721,7 +9721,7 @@
         <v>48</v>
       </c>
       <c r="D382" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E382" s="2" t="s">
         <v>49</v>
@@ -9738,7 +9738,7 @@
         <v>48</v>
       </c>
       <c r="D383" s="2">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E383" s="2" t="s">
         <v>49</v>
@@ -9755,7 +9755,7 @@
         <v>48</v>
       </c>
       <c r="D384" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E384" s="2" t="s">
         <v>49</v>
@@ -9772,7 +9772,7 @@
         <v>48</v>
       </c>
       <c r="D385" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E385" s="2" t="s">
         <v>49</v>
@@ -9789,7 +9789,7 @@
         <v>48</v>
       </c>
       <c r="D386" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E386" s="2" t="s">
         <v>49</v>
@@ -9806,7 +9806,7 @@
         <v>48</v>
       </c>
       <c r="D387" s="2">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E387" s="2" t="s">
         <v>49</v>
@@ -9823,7 +9823,7 @@
         <v>48</v>
       </c>
       <c r="D388" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E388" s="2" t="s">
         <v>49</v>
@@ -9840,7 +9840,7 @@
         <v>48</v>
       </c>
       <c r="D389" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E389" s="2" t="s">
         <v>49</v>
@@ -9874,7 +9874,7 @@
         <v>48</v>
       </c>
       <c r="D391" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E391" s="2" t="s">
         <v>49</v>
@@ -9891,7 +9891,7 @@
         <v>48</v>
       </c>
       <c r="D392" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E392" s="2" t="s">
         <v>49</v>
@@ -9908,7 +9908,7 @@
         <v>48</v>
       </c>
       <c r="D393" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E393" s="2" t="s">
         <v>49</v>
@@ -9925,7 +9925,7 @@
         <v>48</v>
       </c>
       <c r="D394" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E394" s="2" t="s">
         <v>49</v>
@@ -9942,7 +9942,7 @@
         <v>48</v>
       </c>
       <c r="D395" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E395" s="2" t="s">
         <v>49</v>
@@ -9959,7 +9959,7 @@
         <v>48</v>
       </c>
       <c r="D396" s="2">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E396" s="2" t="s">
         <v>49</v>
@@ -9976,7 +9976,7 @@
         <v>48</v>
       </c>
       <c r="D397" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E397" s="2" t="s">
         <v>49</v>
@@ -9993,7 +9993,7 @@
         <v>48</v>
       </c>
       <c r="D398" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E398" s="2" t="s">
         <v>49</v>
@@ -10044,7 +10044,7 @@
         <v>48</v>
       </c>
       <c r="D401" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E401" s="2" t="s">
         <v>49</v>
@@ -10061,7 +10061,7 @@
         <v>48</v>
       </c>
       <c r="D402" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E402" s="2" t="s">
         <v>49</v>
@@ -10078,7 +10078,7 @@
         <v>48</v>
       </c>
       <c r="D403" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E403" s="2" t="s">
         <v>49</v>
@@ -10095,7 +10095,7 @@
         <v>48</v>
       </c>
       <c r="D404" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E404" s="2" t="s">
         <v>49</v>
@@ -10112,7 +10112,7 @@
         <v>48</v>
       </c>
       <c r="D405" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>49</v>
@@ -10129,7 +10129,7 @@
         <v>48</v>
       </c>
       <c r="D406" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E406" s="2" t="s">
         <v>49</v>
@@ -10146,7 +10146,7 @@
         <v>48</v>
       </c>
       <c r="D407" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E407" s="2" t="s">
         <v>49</v>
@@ -10163,7 +10163,7 @@
         <v>48</v>
       </c>
       <c r="D408" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E408" s="2" t="s">
         <v>49</v>
@@ -10180,7 +10180,7 @@
         <v>48</v>
       </c>
       <c r="D409" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E409" s="2" t="s">
         <v>49</v>
@@ -10197,7 +10197,7 @@
         <v>48</v>
       </c>
       <c r="D410" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E410" s="2" t="s">
         <v>49</v>
@@ -10214,7 +10214,7 @@
         <v>48</v>
       </c>
       <c r="D411" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E411" s="2" t="s">
         <v>49</v>
@@ -10231,7 +10231,7 @@
         <v>48</v>
       </c>
       <c r="D412" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E412" s="2" t="s">
         <v>49</v>
@@ -10248,7 +10248,7 @@
         <v>48</v>
       </c>
       <c r="D413" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E413" s="2" t="s">
         <v>49</v>
@@ -10265,7 +10265,7 @@
         <v>48</v>
       </c>
       <c r="D414" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E414" s="2" t="s">
         <v>49</v>
@@ -10282,7 +10282,7 @@
         <v>48</v>
       </c>
       <c r="D415" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E415" s="2" t="s">
         <v>49</v>
@@ -10299,7 +10299,7 @@
         <v>48</v>
       </c>
       <c r="D416" s="2">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E416" s="2" t="s">
         <v>49</v>
@@ -10316,7 +10316,7 @@
         <v>48</v>
       </c>
       <c r="D417" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E417" s="2" t="s">
         <v>49</v>
@@ -10333,7 +10333,7 @@
         <v>48</v>
       </c>
       <c r="D418" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E418" s="2" t="s">
         <v>49</v>
@@ -10350,7 +10350,7 @@
         <v>48</v>
       </c>
       <c r="D419" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E419" s="2" t="s">
         <v>49</v>
@@ -10367,7 +10367,7 @@
         <v>48</v>
       </c>
       <c r="D420" s="2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E420" s="2" t="s">
         <v>49</v>
@@ -10384,7 +10384,7 @@
         <v>48</v>
       </c>
       <c r="D421" s="2">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="E421" s="2" t="s">
         <v>49</v>
@@ -10401,7 +10401,7 @@
         <v>48</v>
       </c>
       <c r="D422" s="2">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E422" s="2" t="s">
         <v>49</v>
@@ -10418,7 +10418,7 @@
         <v>48</v>
       </c>
       <c r="D423" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E423" s="2" t="s">
         <v>49</v>
@@ -10435,7 +10435,7 @@
         <v>48</v>
       </c>
       <c r="D424" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E424" s="2" t="s">
         <v>49</v>
@@ -10452,7 +10452,7 @@
         <v>48</v>
       </c>
       <c r="D425" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E425" s="2" t="s">
         <v>49</v>
@@ -10469,7 +10469,7 @@
         <v>48</v>
       </c>
       <c r="D426" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E426" s="2" t="s">
         <v>49</v>
@@ -10503,7 +10503,7 @@
         <v>48</v>
       </c>
       <c r="D428" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E428" s="2" t="s">
         <v>49</v>
@@ -10520,7 +10520,7 @@
         <v>48</v>
       </c>
       <c r="D429" s="2">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E429" s="2" t="s">
         <v>49</v>
@@ -10537,7 +10537,7 @@
         <v>48</v>
       </c>
       <c r="D430" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E430" s="2" t="s">
         <v>49</v>
@@ -10554,7 +10554,7 @@
         <v>48</v>
       </c>
       <c r="D431" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E431" s="2" t="s">
         <v>49</v>
@@ -10571,7 +10571,7 @@
         <v>48</v>
       </c>
       <c r="D432" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E432" s="2" t="s">
         <v>49</v>
@@ -10588,7 +10588,7 @@
         <v>48</v>
       </c>
       <c r="D433" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E433" s="2" t="s">
         <v>49</v>
@@ -10605,7 +10605,7 @@
         <v>48</v>
       </c>
       <c r="D434" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E434" s="2" t="s">
         <v>49</v>
@@ -10622,7 +10622,7 @@
         <v>48</v>
       </c>
       <c r="D435" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E435" s="2" t="s">
         <v>49</v>
@@ -10639,7 +10639,7 @@
         <v>48</v>
       </c>
       <c r="D436" s="2">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E436" s="2" t="s">
         <v>49</v>
@@ -10656,7 +10656,7 @@
         <v>48</v>
       </c>
       <c r="D437" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E437" s="2" t="s">
         <v>49</v>
@@ -10673,7 +10673,7 @@
         <v>48</v>
       </c>
       <c r="D438" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>49</v>
@@ -10690,7 +10690,7 @@
         <v>48</v>
       </c>
       <c r="D439" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E439" s="2" t="s">
         <v>49</v>
@@ -10707,7 +10707,7 @@
         <v>48</v>
       </c>
       <c r="D440" s="2">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E440" s="2" t="s">
         <v>49</v>
@@ -10724,7 +10724,7 @@
         <v>48</v>
       </c>
       <c r="D441" s="2">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E441" s="2" t="s">
         <v>49</v>
@@ -10741,7 +10741,7 @@
         <v>48</v>
       </c>
       <c r="D442" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E442" s="2" t="s">
         <v>49</v>
@@ -10758,7 +10758,7 @@
         <v>48</v>
       </c>
       <c r="D443" s="2">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="E443" s="2" t="s">
         <v>49</v>
@@ -10775,7 +10775,7 @@
         <v>48</v>
       </c>
       <c r="D444" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E444" s="2" t="s">
         <v>49</v>
@@ -10792,7 +10792,7 @@
         <v>48</v>
       </c>
       <c r="D445" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E445" s="2" t="s">
         <v>49</v>
@@ -10809,7 +10809,7 @@
         <v>48</v>
       </c>
       <c r="D446" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E446" s="2" t="s">
         <v>49</v>
@@ -10826,7 +10826,7 @@
         <v>48</v>
       </c>
       <c r="D447" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E447" s="2" t="s">
         <v>49</v>
@@ -10860,7 +10860,7 @@
         <v>48</v>
       </c>
       <c r="D449" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E449" s="2" t="s">
         <v>49</v>
@@ -10894,7 +10894,7 @@
         <v>48</v>
       </c>
       <c r="D451" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E451" s="2" t="s">
         <v>49</v>
@@ -10911,7 +10911,7 @@
         <v>48</v>
       </c>
       <c r="D452" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E452" s="2" t="s">
         <v>49</v>
@@ -10928,7 +10928,7 @@
         <v>48</v>
       </c>
       <c r="D453" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E453" s="2" t="s">
         <v>49</v>
@@ -10945,7 +10945,7 @@
         <v>48</v>
       </c>
       <c r="D454" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E454" s="2" t="s">
         <v>49</v>
@@ -10962,7 +10962,7 @@
         <v>48</v>
       </c>
       <c r="D455" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E455" s="2" t="s">
         <v>49</v>
@@ -10979,7 +10979,7 @@
         <v>48</v>
       </c>
       <c r="D456" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E456" s="2" t="s">
         <v>49</v>
@@ -10996,7 +10996,7 @@
         <v>48</v>
       </c>
       <c r="D457" s="2">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E457" s="2" t="s">
         <v>49</v>
@@ -11013,7 +11013,7 @@
         <v>48</v>
       </c>
       <c r="D458" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E458" s="2" t="s">
         <v>49</v>
@@ -11030,7 +11030,7 @@
         <v>48</v>
       </c>
       <c r="D459" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E459" s="2" t="s">
         <v>49</v>
@@ -11047,7 +11047,7 @@
         <v>48</v>
       </c>
       <c r="D460" s="2">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E460" s="2" t="s">
         <v>49</v>
@@ -11064,7 +11064,7 @@
         <v>48</v>
       </c>
       <c r="D461" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E461" s="2" t="s">
         <v>49</v>
@@ -11081,7 +11081,7 @@
         <v>48</v>
       </c>
       <c r="D462" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E462" s="2" t="s">
         <v>49</v>
@@ -11098,7 +11098,7 @@
         <v>48</v>
       </c>
       <c r="D463" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E463" s="2" t="s">
         <v>49</v>
@@ -11115,7 +11115,7 @@
         <v>48</v>
       </c>
       <c r="D464" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E464" s="2" t="s">
         <v>49</v>
@@ -11132,7 +11132,7 @@
         <v>48</v>
       </c>
       <c r="D465" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E465" s="2" t="s">
         <v>49</v>
@@ -11149,7 +11149,7 @@
         <v>48</v>
       </c>
       <c r="D466" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E466" s="2" t="s">
         <v>49</v>
@@ -11166,7 +11166,7 @@
         <v>48</v>
       </c>
       <c r="D467" s="2">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E467" s="2" t="s">
         <v>49</v>
@@ -11183,7 +11183,7 @@
         <v>48</v>
       </c>
       <c r="D468" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E468" s="2" t="s">
         <v>49</v>
@@ -11200,7 +11200,7 @@
         <v>48</v>
       </c>
       <c r="D469" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E469" s="2" t="s">
         <v>49</v>
@@ -11234,7 +11234,7 @@
         <v>48</v>
       </c>
       <c r="D471" s="2">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E471" s="2" t="s">
         <v>49</v>
@@ -11251,7 +11251,7 @@
         <v>48</v>
       </c>
       <c r="D472" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E472" s="2" t="s">
         <v>49</v>
@@ -11268,7 +11268,7 @@
         <v>48</v>
       </c>
       <c r="D473" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E473" s="2" t="s">
         <v>49</v>
@@ -11302,7 +11302,7 @@
         <v>48</v>
       </c>
       <c r="D475" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E475" s="2" t="s">
         <v>49</v>
@@ -11319,7 +11319,7 @@
         <v>48</v>
       </c>
       <c r="D476" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>49</v>
@@ -11336,7 +11336,7 @@
         <v>48</v>
       </c>
       <c r="D477" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>49</v>
@@ -11370,7 +11370,7 @@
         <v>48</v>
       </c>
       <c r="D479" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E479" s="2" t="s">
         <v>49</v>
@@ -11387,7 +11387,7 @@
         <v>48</v>
       </c>
       <c r="D480" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E480" s="2" t="s">
         <v>49</v>
@@ -11404,7 +11404,7 @@
         <v>48</v>
       </c>
       <c r="D481" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E481" s="2" t="s">
         <v>49</v>
@@ -11421,7 +11421,7 @@
         <v>48</v>
       </c>
       <c r="D482" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E482" s="2" t="s">
         <v>49</v>
@@ -11438,7 +11438,7 @@
         <v>48</v>
       </c>
       <c r="D483" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E483" s="2" t="s">
         <v>49</v>
@@ -11455,7 +11455,7 @@
         <v>48</v>
       </c>
       <c r="D484" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E484" s="2" t="s">
         <v>49</v>
@@ -11472,7 +11472,7 @@
         <v>48</v>
       </c>
       <c r="D485" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>49</v>
@@ -11489,7 +11489,7 @@
         <v>48</v>
       </c>
       <c r="D486" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>49</v>
@@ -11506,7 +11506,7 @@
         <v>48</v>
       </c>
       <c r="D487" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E487" s="2" t="s">
         <v>49</v>
@@ -11523,7 +11523,7 @@
         <v>48</v>
       </c>
       <c r="D488" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E488" s="2" t="s">
         <v>49</v>
@@ -11540,7 +11540,7 @@
         <v>48</v>
       </c>
       <c r="D489" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E489" s="2" t="s">
         <v>49</v>
@@ -11557,7 +11557,7 @@
         <v>48</v>
       </c>
       <c r="D490" s="2">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E490" s="2" t="s">
         <v>49</v>
@@ -11574,7 +11574,7 @@
         <v>48</v>
       </c>
       <c r="D491" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E491" s="2" t="s">
         <v>49</v>
@@ -11591,7 +11591,7 @@
         <v>48</v>
       </c>
       <c r="D492" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E492" s="2" t="s">
         <v>49</v>
@@ -11608,7 +11608,7 @@
         <v>48</v>
       </c>
       <c r="D493" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>49</v>
@@ -11625,7 +11625,7 @@
         <v>48</v>
       </c>
       <c r="D494" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E494" s="2" t="s">
         <v>49</v>
@@ -11642,7 +11642,7 @@
         <v>48</v>
       </c>
       <c r="D495" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E495" s="2" t="s">
         <v>49</v>
@@ -11676,7 +11676,7 @@
         <v>48</v>
       </c>
       <c r="D497" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>49</v>
@@ -11693,7 +11693,7 @@
         <v>48</v>
       </c>
       <c r="D498" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E498" s="2" t="s">
         <v>49</v>
@@ -11710,7 +11710,7 @@
         <v>48</v>
       </c>
       <c r="D499" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E499" s="2" t="s">
         <v>49</v>
@@ -11727,7 +11727,7 @@
         <v>48</v>
       </c>
       <c r="D500" s="2">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E500" s="2" t="s">
         <v>49</v>
@@ -11744,7 +11744,7 @@
         <v>48</v>
       </c>
       <c r="D501" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E501" s="2" t="s">
         <v>49</v>
@@ -11761,7 +11761,7 @@
         <v>48</v>
       </c>
       <c r="D502" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E502" s="2" t="s">
         <v>49</v>
@@ -11778,7 +11778,7 @@
         <v>48</v>
       </c>
       <c r="D503" s="2">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="E503" s="2" t="s">
         <v>49</v>
@@ -11795,7 +11795,7 @@
         <v>48</v>
       </c>
       <c r="D504" s="2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E504" s="2" t="s">
         <v>49</v>
@@ -11829,7 +11829,7 @@
         <v>48</v>
       </c>
       <c r="D506" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E506" s="2" t="s">
         <v>49</v>
@@ -11846,7 +11846,7 @@
         <v>48</v>
       </c>
       <c r="D507" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E507" s="2" t="s">
         <v>49</v>
@@ -11863,7 +11863,7 @@
         <v>48</v>
       </c>
       <c r="D508" s="2">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E508" s="2" t="s">
         <v>49</v>
@@ -11897,7 +11897,7 @@
         <v>48</v>
       </c>
       <c r="D510" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E510" s="2" t="s">
         <v>49</v>
@@ -11914,7 +11914,7 @@
         <v>48</v>
       </c>
       <c r="D511" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E511" s="2" t="s">
         <v>49</v>
@@ -11931,7 +11931,7 @@
         <v>48</v>
       </c>
       <c r="D512" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E512" s="2" t="s">
         <v>49</v>
@@ -11948,7 +11948,7 @@
         <v>48</v>
       </c>
       <c r="D513" s="2">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="E513" s="2" t="s">
         <v>49</v>
@@ -11965,7 +11965,7 @@
         <v>48</v>
       </c>
       <c r="D514" s="2">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E514" s="2" t="s">
         <v>49</v>
@@ -11982,7 +11982,7 @@
         <v>48</v>
       </c>
       <c r="D515" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E515" s="2" t="s">
         <v>49</v>
@@ -11999,7 +11999,7 @@
         <v>48</v>
       </c>
       <c r="D516" s="2">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E516" s="2" t="s">
         <v>49</v>
@@ -12033,7 +12033,7 @@
         <v>48</v>
       </c>
       <c r="D518" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>49</v>
@@ -12050,7 +12050,7 @@
         <v>48</v>
       </c>
       <c r="D519" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>49</v>
@@ -12067,7 +12067,7 @@
         <v>48</v>
       </c>
       <c r="D520" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>49</v>
@@ -12084,7 +12084,7 @@
         <v>48</v>
       </c>
       <c r="D521" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>49</v>
@@ -12101,7 +12101,7 @@
         <v>48</v>
       </c>
       <c r="D522" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>49</v>
@@ -12118,7 +12118,7 @@
         <v>48</v>
       </c>
       <c r="D523" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E523" s="2" t="s">
         <v>49</v>
@@ -12135,7 +12135,7 @@
         <v>48</v>
       </c>
       <c r="D524" s="2">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="E524" s="2" t="s">
         <v>49</v>
@@ -12152,7 +12152,7 @@
         <v>48</v>
       </c>
       <c r="D525" s="2">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E525" s="2" t="s">
         <v>49</v>
@@ -12169,7 +12169,7 @@
         <v>48</v>
       </c>
       <c r="D526" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E526" s="2" t="s">
         <v>49</v>
@@ -12186,7 +12186,7 @@
         <v>48</v>
       </c>
       <c r="D527" s="2">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="E527" s="2" t="s">
         <v>49</v>
@@ -12203,7 +12203,7 @@
         <v>48</v>
       </c>
       <c r="D528" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E528" s="2" t="s">
         <v>49</v>
@@ -12220,7 +12220,7 @@
         <v>48</v>
       </c>
       <c r="D529" s="2">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E529" s="2" t="s">
         <v>49</v>
@@ -12237,7 +12237,7 @@
         <v>48</v>
       </c>
       <c r="D530" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E530" s="2" t="s">
         <v>49</v>
@@ -12254,7 +12254,7 @@
         <v>48</v>
       </c>
       <c r="D531" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E531" s="2" t="s">
         <v>49</v>
@@ -12271,7 +12271,7 @@
         <v>48</v>
       </c>
       <c r="D532" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E532" s="2" t="s">
         <v>49</v>
@@ -12288,7 +12288,7 @@
         <v>48</v>
       </c>
       <c r="D533" s="2">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="E533" s="2" t="s">
         <v>49</v>
@@ -12305,7 +12305,7 @@
         <v>48</v>
       </c>
       <c r="D534" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E534" s="2" t="s">
         <v>49</v>
@@ -12322,7 +12322,7 @@
         <v>48</v>
       </c>
       <c r="D535" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E535" s="2" t="s">
         <v>49</v>
@@ -12339,7 +12339,7 @@
         <v>48</v>
       </c>
       <c r="D536" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E536" s="2" t="s">
         <v>49</v>
@@ -12356,7 +12356,7 @@
         <v>48</v>
       </c>
       <c r="D537" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E537" s="2" t="s">
         <v>49</v>
@@ -12373,7 +12373,7 @@
         <v>48</v>
       </c>
       <c r="D538" s="2">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E538" s="2" t="s">
         <v>49</v>
@@ -12390,7 +12390,7 @@
         <v>48</v>
       </c>
       <c r="D539" s="2">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E539" s="2" t="s">
         <v>49</v>
@@ -12407,7 +12407,7 @@
         <v>48</v>
       </c>
       <c r="D540" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E540" s="2" t="s">
         <v>49</v>
@@ -12424,7 +12424,7 @@
         <v>48</v>
       </c>
       <c r="D541" s="2">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="E541" s="2" t="s">
         <v>49</v>
@@ -12441,7 +12441,7 @@
         <v>48</v>
       </c>
       <c r="D542" s="2">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E542" s="2" t="s">
         <v>49</v>
@@ -12458,7 +12458,7 @@
         <v>48</v>
       </c>
       <c r="D543" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E543" s="2" t="s">
         <v>49</v>
@@ -12475,7 +12475,7 @@
         <v>48</v>
       </c>
       <c r="D544" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>49</v>
@@ -12492,7 +12492,7 @@
         <v>48</v>
       </c>
       <c r="D545" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E545" s="2" t="s">
         <v>49</v>
@@ -12509,7 +12509,7 @@
         <v>48</v>
       </c>
       <c r="D546" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E546" s="2" t="s">
         <v>49</v>
@@ -12526,7 +12526,7 @@
         <v>48</v>
       </c>
       <c r="D547" s="2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E547" s="2" t="s">
         <v>49</v>
@@ -12543,7 +12543,7 @@
         <v>48</v>
       </c>
       <c r="D548" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>49</v>
@@ -12560,7 +12560,7 @@
         <v>48</v>
       </c>
       <c r="D549" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E549" s="2" t="s">
         <v>49</v>
@@ -12577,7 +12577,7 @@
         <v>48</v>
       </c>
       <c r="D550" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E550" s="2" t="s">
         <v>49</v>
@@ -12611,7 +12611,7 @@
         <v>48</v>
       </c>
       <c r="D552" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>49</v>
@@ -12628,7 +12628,7 @@
         <v>48</v>
       </c>
       <c r="D553" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>49</v>
@@ -12645,7 +12645,7 @@
         <v>48</v>
       </c>
       <c r="D554" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E554" s="2" t="s">
         <v>49</v>
@@ -12662,7 +12662,7 @@
         <v>48</v>
       </c>
       <c r="D555" s="2">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E555" s="2" t="s">
         <v>49</v>
@@ -12679,7 +12679,7 @@
         <v>48</v>
       </c>
       <c r="D556" s="2">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E556" s="2" t="s">
         <v>49</v>
@@ -12696,7 +12696,7 @@
         <v>48</v>
       </c>
       <c r="D557" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E557" s="2" t="s">
         <v>49</v>
@@ -12713,7 +12713,7 @@
         <v>48</v>
       </c>
       <c r="D558" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E558" s="2" t="s">
         <v>49</v>
@@ -12730,7 +12730,7 @@
         <v>48</v>
       </c>
       <c r="D559" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E559" s="2" t="s">
         <v>49</v>
@@ -12747,7 +12747,7 @@
         <v>48</v>
       </c>
       <c r="D560" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>49</v>
@@ -12764,7 +12764,7 @@
         <v>48</v>
       </c>
       <c r="D561" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E561" s="2" t="s">
         <v>49</v>
@@ -12781,7 +12781,7 @@
         <v>48</v>
       </c>
       <c r="D562" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E562" s="2" t="s">
         <v>49</v>
@@ -12798,7 +12798,7 @@
         <v>48</v>
       </c>
       <c r="D563" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E563" s="2" t="s">
         <v>49</v>
@@ -12815,7 +12815,7 @@
         <v>48</v>
       </c>
       <c r="D564" s="2">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E564" s="2" t="s">
         <v>49</v>
@@ -12832,7 +12832,7 @@
         <v>48</v>
       </c>
       <c r="D565" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E565" s="2" t="s">
         <v>49</v>
@@ -12849,7 +12849,7 @@
         <v>48</v>
       </c>
       <c r="D566" s="2">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="E566" s="2" t="s">
         <v>49</v>
@@ -12866,7 +12866,7 @@
         <v>48</v>
       </c>
       <c r="D567" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E567" s="2" t="s">
         <v>49</v>
@@ -12883,7 +12883,7 @@
         <v>48</v>
       </c>
       <c r="D568" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="E568" s="2" t="s">
         <v>49</v>
@@ -12900,7 +12900,7 @@
         <v>48</v>
       </c>
       <c r="D569" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E569" s="2" t="s">
         <v>49</v>
@@ -12917,7 +12917,7 @@
         <v>48</v>
       </c>
       <c r="D570" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E570" s="2" t="s">
         <v>49</v>
@@ -12934,7 +12934,7 @@
         <v>48</v>
       </c>
       <c r="D571" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E571" s="2" t="s">
         <v>49</v>
@@ -12951,7 +12951,7 @@
         <v>48</v>
       </c>
       <c r="D572" s="2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E572" s="2" t="s">
         <v>49</v>
@@ -12968,7 +12968,7 @@
         <v>48</v>
       </c>
       <c r="D573" s="2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E573" s="2" t="s">
         <v>49</v>
@@ -12985,7 +12985,7 @@
         <v>48</v>
       </c>
       <c r="D574" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>49</v>
@@ -13002,7 +13002,7 @@
         <v>48</v>
       </c>
       <c r="D575" s="2">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>49</v>
@@ -13019,7 +13019,7 @@
         <v>48</v>
       </c>
       <c r="D576" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E576" s="2" t="s">
         <v>49</v>
@@ -13036,7 +13036,7 @@
         <v>48</v>
       </c>
       <c r="D577" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E577" s="2" t="s">
         <v>49</v>
@@ -13053,7 +13053,7 @@
         <v>48</v>
       </c>
       <c r="D578" s="2">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E578" s="2" t="s">
         <v>49</v>
@@ -13070,7 +13070,7 @@
         <v>48</v>
       </c>
       <c r="D579" s="2">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E579" s="2" t="s">
         <v>49</v>
@@ -13087,7 +13087,7 @@
         <v>48</v>
       </c>
       <c r="D580" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E580" s="2" t="s">
         <v>49</v>
@@ -13104,7 +13104,7 @@
         <v>48</v>
       </c>
       <c r="D581" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E581" s="2" t="s">
         <v>49</v>
@@ -13121,7 +13121,7 @@
         <v>48</v>
       </c>
       <c r="D582" s="2">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="E582" s="2" t="s">
         <v>49</v>
@@ -13138,7 +13138,7 @@
         <v>48</v>
       </c>
       <c r="D583" s="2">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="E583" s="2" t="s">
         <v>49</v>
@@ -13155,7 +13155,7 @@
         <v>48</v>
       </c>
       <c r="D584" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E584" s="2" t="s">
         <v>49</v>
@@ -13172,7 +13172,7 @@
         <v>48</v>
       </c>
       <c r="D585" s="2">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E585" s="2" t="s">
         <v>49</v>
@@ -13189,7 +13189,7 @@
         <v>48</v>
       </c>
       <c r="D586" s="2">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="E586" s="2" t="s">
         <v>49</v>
@@ -13206,7 +13206,7 @@
         <v>48</v>
       </c>
       <c r="D587" s="2">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E587" s="2" t="s">
         <v>49</v>
@@ -13240,7 +13240,7 @@
         <v>48</v>
       </c>
       <c r="D589" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E589" s="2" t="s">
         <v>49</v>
@@ -13257,7 +13257,7 @@
         <v>48</v>
       </c>
       <c r="D590" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E590" s="2" t="s">
         <v>49</v>
@@ -13274,7 +13274,7 @@
         <v>48</v>
       </c>
       <c r="D591" s="2">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>49</v>
@@ -13291,7 +13291,7 @@
         <v>48</v>
       </c>
       <c r="D592" s="2">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E592" s="2" t="s">
         <v>49</v>
@@ -13308,7 +13308,7 @@
         <v>48</v>
       </c>
       <c r="D593" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E593" s="2" t="s">
         <v>49</v>
@@ -13325,7 +13325,7 @@
         <v>48</v>
       </c>
       <c r="D594" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E594" s="2" t="s">
         <v>49</v>
@@ -13342,7 +13342,7 @@
         <v>48</v>
       </c>
       <c r="D595" s="2">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="E595" s="2" t="s">
         <v>49</v>
@@ -13359,7 +13359,7 @@
         <v>48</v>
       </c>
       <c r="D596" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E596" s="2" t="s">
         <v>49</v>
@@ -13376,7 +13376,7 @@
         <v>48</v>
       </c>
       <c r="D597" s="2">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E597" s="2" t="s">
         <v>49</v>
@@ -13393,7 +13393,7 @@
         <v>48</v>
       </c>
       <c r="D598" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E598" s="2" t="s">
         <v>49</v>
@@ -13410,7 +13410,7 @@
         <v>48</v>
       </c>
       <c r="D599" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E599" s="2" t="s">
         <v>49</v>
@@ -13427,7 +13427,7 @@
         <v>48</v>
       </c>
       <c r="D600" s="2">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E600" s="2" t="s">
         <v>49</v>
@@ -13444,7 +13444,7 @@
         <v>48</v>
       </c>
       <c r="D601" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E601" s="2" t="s">
         <v>49</v>
@@ -13461,7 +13461,7 @@
         <v>48</v>
       </c>
       <c r="D602" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E602" s="2" t="s">
         <v>49</v>
@@ -13478,7 +13478,7 @@
         <v>48</v>
       </c>
       <c r="D603" s="2">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="E603" s="2" t="s">
         <v>49</v>
@@ -13495,7 +13495,7 @@
         <v>48</v>
       </c>
       <c r="D604" s="2">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>49</v>
@@ -13512,7 +13512,7 @@
         <v>48</v>
       </c>
       <c r="D605" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E605" s="2" t="s">
         <v>49</v>
@@ -13529,7 +13529,7 @@
         <v>48</v>
       </c>
       <c r="D606" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E606" s="2" t="s">
         <v>49</v>
@@ -13546,7 +13546,7 @@
         <v>48</v>
       </c>
       <c r="D607" s="2">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E607" s="2" t="s">
         <v>49</v>
@@ -13563,7 +13563,7 @@
         <v>48</v>
       </c>
       <c r="D608" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E608" s="2" t="s">
         <v>49</v>
@@ -13597,7 +13597,7 @@
         <v>48</v>
       </c>
       <c r="D610" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>49</v>
@@ -13614,7 +13614,7 @@
         <v>48</v>
       </c>
       <c r="D611" s="2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E611" s="2" t="s">
         <v>49</v>
@@ -13631,7 +13631,7 @@
         <v>48</v>
       </c>
       <c r="D612" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E612" s="2" t="s">
         <v>49</v>
@@ -13648,7 +13648,7 @@
         <v>48</v>
       </c>
       <c r="D613" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E613" s="2" t="s">
         <v>49</v>
@@ -13682,7 +13682,7 @@
         <v>48</v>
       </c>
       <c r="D615" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E615" s="2" t="s">
         <v>49</v>
@@ -13699,7 +13699,7 @@
         <v>48</v>
       </c>
       <c r="D616" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E616" s="2" t="s">
         <v>49</v>
@@ -13716,7 +13716,7 @@
         <v>48</v>
       </c>
       <c r="D617" s="2">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="E617" s="2" t="s">
         <v>49</v>
@@ -13733,7 +13733,7 @@
         <v>48</v>
       </c>
       <c r="D618" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E618" s="2" t="s">
         <v>49</v>
@@ -13750,7 +13750,7 @@
         <v>48</v>
       </c>
       <c r="D619" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E619" s="2" t="s">
         <v>49</v>
@@ -13767,7 +13767,7 @@
         <v>48</v>
       </c>
       <c r="D620" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E620" s="2" t="s">
         <v>49</v>
@@ -13784,7 +13784,7 @@
         <v>48</v>
       </c>
       <c r="D621" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E621" s="2" t="s">
         <v>49</v>
@@ -13801,7 +13801,7 @@
         <v>48</v>
       </c>
       <c r="D622" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E622" s="2" t="s">
         <v>49</v>
@@ -13818,7 +13818,7 @@
         <v>48</v>
       </c>
       <c r="D623" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E623" s="2" t="s">
         <v>49</v>
@@ -13835,7 +13835,7 @@
         <v>48</v>
       </c>
       <c r="D624" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E624" s="2" t="s">
         <v>49</v>
@@ -13852,7 +13852,7 @@
         <v>48</v>
       </c>
       <c r="D625" s="2">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E625" s="2" t="s">
         <v>49</v>
@@ -13869,7 +13869,7 @@
         <v>48</v>
       </c>
       <c r="D626" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E626" s="2" t="s">
         <v>49</v>
@@ -13886,7 +13886,7 @@
         <v>48</v>
       </c>
       <c r="D627" s="2">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="E627" s="2" t="s">
         <v>49</v>
@@ -13903,7 +13903,7 @@
         <v>48</v>
       </c>
       <c r="D628" s="2">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E628" s="2" t="s">
         <v>49</v>
@@ -13920,7 +13920,7 @@
         <v>48</v>
       </c>
       <c r="D629" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E629" s="2" t="s">
         <v>49</v>
@@ -13937,7 +13937,7 @@
         <v>48</v>
       </c>
       <c r="D630" s="2">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="E630" s="2" t="s">
         <v>49</v>
@@ -13954,7 +13954,7 @@
         <v>48</v>
       </c>
       <c r="D631" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E631" s="2" t="s">
         <v>49</v>
@@ -13971,7 +13971,7 @@
         <v>48</v>
       </c>
       <c r="D632" s="2">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E632" s="2" t="s">
         <v>49</v>
@@ -13988,7 +13988,7 @@
         <v>48</v>
       </c>
       <c r="D633" s="2">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="E633" s="2" t="s">
         <v>49</v>
@@ -14005,7 +14005,7 @@
         <v>48</v>
       </c>
       <c r="D634" s="2">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E634" s="2" t="s">
         <v>49</v>
@@ -14022,7 +14022,7 @@
         <v>48</v>
       </c>
       <c r="D635" s="2">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E635" s="2" t="s">
         <v>49</v>
@@ -14039,7 +14039,7 @@
         <v>48</v>
       </c>
       <c r="D636" s="2">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E636" s="2" t="s">
         <v>49</v>
@@ -14056,7 +14056,7 @@
         <v>48</v>
       </c>
       <c r="D637" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>49</v>
@@ -14073,7 +14073,7 @@
         <v>48</v>
       </c>
       <c r="D638" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E638" s="2" t="s">
         <v>49</v>
@@ -14090,7 +14090,7 @@
         <v>48</v>
       </c>
       <c r="D639" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E639" s="2" t="s">
         <v>49</v>
@@ -14107,7 +14107,7 @@
         <v>48</v>
       </c>
       <c r="D640" s="2">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E640" s="2" t="s">
         <v>49</v>
@@ -14124,7 +14124,7 @@
         <v>48</v>
       </c>
       <c r="D641" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>49</v>
@@ -14141,7 +14141,7 @@
         <v>48</v>
       </c>
       <c r="D642" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E642" s="2" t="s">
         <v>49</v>
@@ -14158,7 +14158,7 @@
         <v>48</v>
       </c>
       <c r="D643" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E643" s="2" t="s">
         <v>49</v>
@@ -14175,7 +14175,7 @@
         <v>48</v>
       </c>
       <c r="D644" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E644" s="2" t="s">
         <v>49</v>
@@ -14192,7 +14192,7 @@
         <v>48</v>
       </c>
       <c r="D645" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E645" s="2" t="s">
         <v>49</v>
@@ -14209,7 +14209,7 @@
         <v>48</v>
       </c>
       <c r="D646" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="E646" s="2" t="s">
         <v>49</v>
@@ -14226,7 +14226,7 @@
         <v>48</v>
       </c>
       <c r="D647" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E647" s="2" t="s">
         <v>49</v>
@@ -14243,7 +14243,7 @@
         <v>48</v>
       </c>
       <c r="D648" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E648" s="2" t="s">
         <v>49</v>
@@ -14260,7 +14260,7 @@
         <v>48</v>
       </c>
       <c r="D649" s="2">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="E649" s="2" t="s">
         <v>49</v>
@@ -14277,7 +14277,7 @@
         <v>48</v>
       </c>
       <c r="D650" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E650" s="2" t="s">
         <v>49</v>
@@ -14294,7 +14294,7 @@
         <v>48</v>
       </c>
       <c r="D651" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E651" s="2" t="s">
         <v>49</v>
@@ -14311,7 +14311,7 @@
         <v>48</v>
       </c>
       <c r="D652" s="2">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E652" s="2" t="s">
         <v>49</v>
@@ -14328,7 +14328,7 @@
         <v>48</v>
       </c>
       <c r="D653" s="2">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E653" s="2" t="s">
         <v>49</v>
@@ -14345,7 +14345,7 @@
         <v>48</v>
       </c>
       <c r="D654" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E654" s="2" t="s">
         <v>49</v>
@@ -14362,7 +14362,7 @@
         <v>48</v>
       </c>
       <c r="D655" s="2">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E655" s="2" t="s">
         <v>49</v>
@@ -14379,7 +14379,7 @@
         <v>48</v>
       </c>
       <c r="D656" s="2">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="E656" s="2" t="s">
         <v>49</v>
@@ -14396,7 +14396,7 @@
         <v>48</v>
       </c>
       <c r="D657" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E657" s="2" t="s">
         <v>49</v>
@@ -14413,7 +14413,7 @@
         <v>48</v>
       </c>
       <c r="D658" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E658" s="2" t="s">
         <v>49</v>
@@ -14430,7 +14430,7 @@
         <v>48</v>
       </c>
       <c r="D659" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E659" s="2" t="s">
         <v>49</v>
@@ -14447,7 +14447,7 @@
         <v>48</v>
       </c>
       <c r="D660" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E660" s="2" t="s">
         <v>49</v>
@@ -14464,7 +14464,7 @@
         <v>48</v>
       </c>
       <c r="D661" s="2">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E661" s="2" t="s">
         <v>49</v>
@@ -14481,7 +14481,7 @@
         <v>48</v>
       </c>
       <c r="D662" s="2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E662" s="2" t="s">
         <v>49</v>
@@ -14498,7 +14498,7 @@
         <v>48</v>
       </c>
       <c r="D663" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E663" s="2" t="s">
         <v>49</v>
@@ -14515,7 +14515,7 @@
         <v>48</v>
       </c>
       <c r="D664" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E664" s="2" t="s">
         <v>49</v>
@@ -14532,7 +14532,7 @@
         <v>48</v>
       </c>
       <c r="D665" s="2">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="E665" s="2" t="s">
         <v>49</v>
@@ -14549,7 +14549,7 @@
         <v>48</v>
       </c>
       <c r="D666" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E666" s="2" t="s">
         <v>49</v>
@@ -14566,7 +14566,7 @@
         <v>48</v>
       </c>
       <c r="D667" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E667" s="2" t="s">
         <v>49</v>
@@ -14600,7 +14600,7 @@
         <v>48</v>
       </c>
       <c r="D669" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E669" s="2" t="s">
         <v>49</v>
@@ -14617,7 +14617,7 @@
         <v>48</v>
       </c>
       <c r="D670" s="2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E670" s="2" t="s">
         <v>49</v>
@@ -14634,7 +14634,7 @@
         <v>48</v>
       </c>
       <c r="D671" s="2">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="E671" s="2" t="s">
         <v>49</v>
@@ -14651,7 +14651,7 @@
         <v>48</v>
       </c>
       <c r="D672" s="2">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E672" s="2" t="s">
         <v>49</v>
@@ -14668,7 +14668,7 @@
         <v>48</v>
       </c>
       <c r="D673" s="2">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="E673" s="2" t="s">
         <v>49</v>
@@ -14685,7 +14685,7 @@
         <v>48</v>
       </c>
       <c r="D674" s="2">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E674" s="2" t="s">
         <v>49</v>
@@ -14702,7 +14702,7 @@
         <v>48</v>
       </c>
       <c r="D675" s="2">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E675" s="2" t="s">
         <v>49</v>
@@ -14719,7 +14719,7 @@
         <v>48</v>
       </c>
       <c r="D676" s="2">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E676" s="2" t="s">
         <v>49</v>
@@ -14736,7 +14736,7 @@
         <v>48</v>
       </c>
       <c r="D677" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E677" s="2" t="s">
         <v>49</v>
@@ -14753,7 +14753,7 @@
         <v>48</v>
       </c>
       <c r="D678" s="2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E678" s="2" t="s">
         <v>49</v>
@@ -14770,7 +14770,7 @@
         <v>48</v>
       </c>
       <c r="D679" s="2">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E679" s="2" t="s">
         <v>49</v>
@@ -14804,7 +14804,7 @@
         <v>48</v>
       </c>
       <c r="D681" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>49</v>
@@ -14821,7 +14821,7 @@
         <v>48</v>
       </c>
       <c r="D682" s="2">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E682" s="2" t="s">
         <v>49</v>
@@ -14838,7 +14838,7 @@
         <v>48</v>
       </c>
       <c r="D683" s="2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="E683" s="2" t="s">
         <v>49</v>
@@ -14855,7 +14855,7 @@
         <v>48</v>
       </c>
       <c r="D684" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E684" s="2" t="s">
         <v>49</v>
@@ -14872,7 +14872,7 @@
         <v>48</v>
       </c>
       <c r="D685" s="2">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E685" s="2" t="s">
         <v>49</v>
@@ -14889,7 +14889,7 @@
         <v>48</v>
       </c>
       <c r="D686" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E686" s="2" t="s">
         <v>49</v>
@@ -14906,7 +14906,7 @@
         <v>48</v>
       </c>
       <c r="D687" s="2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E687" s="2" t="s">
         <v>49</v>
@@ -14923,7 +14923,7 @@
         <v>48</v>
       </c>
       <c r="D688" s="2">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E688" s="2" t="s">
         <v>49</v>
@@ -14940,7 +14940,7 @@
         <v>48</v>
       </c>
       <c r="D689" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E689" s="2" t="s">
         <v>49</v>
@@ -14957,7 +14957,7 @@
         <v>48</v>
       </c>
       <c r="D690" s="2">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E690" s="2" t="s">
         <v>49</v>
@@ -14974,7 +14974,7 @@
         <v>48</v>
       </c>
       <c r="D691" s="2">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E691" s="2" t="s">
         <v>49</v>
@@ -14991,7 +14991,7 @@
         <v>48</v>
       </c>
       <c r="D692" s="2">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E692" s="2" t="s">
         <v>49</v>
@@ -15008,7 +15008,7 @@
         <v>48</v>
       </c>
       <c r="D693" s="2">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="E693" s="2" t="s">
         <v>49</v>
